--- a/Data/Hires/TestDataSloveniaMKv1.xlsx
+++ b/Data/Hires/TestDataSloveniaMKv1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="187">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,166 +229,164 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>Test failed for 'Braulio Wuckert' Employee: Errors and AlertsAlertsGovernment IDs (Row 1)Enter an identifier that isn't already in use.National IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-14T05-24-01-376Z.png</t>
+    <t>795 Store Management (Zogop Dogegy (10185858))</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Jeffrey</t>
+  </si>
+  <si>
+    <t>Crona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070-417-626 </t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Ljubljana</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@email.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>Auto 72978257</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>5 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
+  </si>
+  <si>
+    <t>Asistent v prodaji</t>
+  </si>
+  <si>
+    <t>IV.</t>
+  </si>
+  <si>
+    <t>Unique Master Citizen Number</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>01/01/2045</t>
+  </si>
+  <si>
+    <t>Slovenia Tax Number</t>
+  </si>
+  <si>
+    <t>01/01/2041</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Citizen (Slovenia)</t>
+  </si>
+  <si>
+    <t>TestBankOFSlovenia</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>SI56 2633 0001 2039 086</t>
+  </si>
+  <si>
+    <t>Grun Frun</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>SVN Monthly</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Liana Hodkiewicz' Employee:{undefined}Error: [31mTimed out 5000ms waiting for [39m[2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m()[22m
+Locator: locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')
+Expected: visible
+Received: &lt;element(s) not found&gt;
+Call log:
+  [2m- expect.toBeVisible with timeout 5000ms[22m
+[2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')[22m
+</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>795 Store Management (Zogop Dogegy (10185858))</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Braulio</t>
-  </si>
-  <si>
-    <t>Wuckert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070-417-626 </t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Ljubljana</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@email.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>Auto 27592482</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>5 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
-  </si>
-  <si>
-    <t>Asistent v prodaji</t>
-  </si>
-  <si>
-    <t>IV.</t>
-  </si>
-  <si>
-    <t>Unique Master Citizen Number</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>01/01/2045</t>
-  </si>
-  <si>
-    <t>Slovenia Tax Number</t>
-  </si>
-  <si>
-    <t>01/01/2041</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Citizen (Slovenia)</t>
-  </si>
-  <si>
-    <t>TestBankOFSlovenia</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>SI56 2633 0001 2039 086</t>
-  </si>
-  <si>
-    <t>Grun Frun</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>SVN Monthly</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Maegan Ratke' Employee:{10697867}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Assign Paygroup for Payroll: Maegan Ratke')[22m
-</t>
+    <t>795 Recruitment (Zosig Depazi (10280602))</t>
+  </si>
+  <si>
+    <t>Stacey</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Test3</t>
   </si>
   <si>
     <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
   </si>
   <si>
-    <t>Maegan</t>
-  </si>
-  <si>
-    <t>Ratke</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Test3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Alden Kutch' Employee:{10697869}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Assign Paygroup for Payroll: Alden Kutch')[22m
-</t>
-  </si>
-  <si>
-    <t>Alden</t>
-  </si>
-  <si>
-    <t>Kutch</t>
+    <t>Karine</t>
+  </si>
+  <si>
+    <t>Ruecker</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -406,9 +404,6 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>Test failed for 'Sincere Gusikowski' Employee: Errors and AlertsAlertsGovernment IDs (Row 1)Enter an identifier that isn't already in use.National IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-14T08-22-35-719Z.png</t>
-  </si>
-  <si>
     <t>Sincere</t>
   </si>
   <si>
@@ -427,12 +422,6 @@
     <t>Test5</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Jarrett Blick' Employee:{10697875}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//div[@data-automation-id=\'titleText\'][contains(./text(),\'Personal Information Change: Jarrett Blick\')]')[22m
-</t>
-  </si>
-  <si>
     <t>Jarrett</t>
   </si>
   <si>
@@ -446,12 +435,6 @@
   </si>
   <si>
     <t>Test6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Maximo Nienow' Employee:{10697879}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Assign Paygroup for Payroll: Maximo Nienow')[22m
-</t>
   </si>
   <si>
     <t>Maximo</t>
@@ -574,6 +557,18 @@
     <t>Test14</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Branson Kirlin' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Work Shift')[22m
+</t>
+  </si>
+  <si>
+    <t>Branson</t>
+  </si>
+  <si>
+    <t>Kirlin</t>
+  </si>
+  <si>
     <t>Retail Assistant Stockroom_NEW</t>
   </si>
   <si>
@@ -581,6 +576,16 @@
   </si>
   <si>
     <t>Test15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Keeley Welch' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.
+- Grade Profile is Missing     (Employee Compensation Event For Hire Employee)Alerts &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-18T05-49-41-141Z.png</t>
+  </si>
+  <si>
+    <t>Keeley</t>
+  </si>
+  <si>
+    <t>Welch</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Supervisor_NEW</t>
@@ -1406,121 +1411,117 @@
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="I2" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K2" s="17">
         <f t="shared" ref="K2:K16" si="0">TODAY()-7</f>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U2" s="22">
         <f t="shared" ref="U2:U16" si="1">TODAY()-31</f>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V2" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="X2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="Y2" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="X2" s="24" t="s">
+      <c r="Z2" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y2" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG2" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AH2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF2" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG2" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI2" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ2" s="17">
         <f t="shared" ref="AJ2:AL16" si="2">TODAY()-31</f>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK2" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL2" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM16" si="3">AF2</f>
@@ -1533,86 +1534,86 @@
         <v>251</v>
       </c>
       <c r="AP2" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ2" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR2" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ2" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR2" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS2" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT2" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU2" s="17">
         <f t="shared" ref="AU2:AU16" si="4">TODAY()+7</f>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW2" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX2" s="30">
+        <v>2973000506964</v>
+      </c>
+      <c r="AY2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX2" s="30">
-        <v>2973000506950</v>
-      </c>
-      <c r="AY2" s="17" t="s">
+      <c r="BA2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB2" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ2" s="17" t="s">
+      <c r="BC2" s="31">
+        <v>93300889</v>
+      </c>
+      <c r="BD2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB2" s="29" t="s">
+      <c r="BF2" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BC2" s="31">
-        <v>93300875</v>
-      </c>
-      <c r="BD2" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE2" s="17" t="s">
+      <c r="BG2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH2" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF2" s="19" t="s">
+      <c r="BI2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ2" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH2" s="13" t="s">
+      <c r="BK2" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ2" s="13" t="s">
+      <c r="BM2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK2" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL2" s="13" t="s">
+      <c r="BN2" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM2" s="33" t="s">
+      <c r="BO2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP2" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN2" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ2" s="34">
         <v>99730</v>
@@ -1628,223 +1629,223 @@
       </c>
       <c r="BU2" s="22">
         <f t="shared" ref="BU2:BU16" si="5">TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV2" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>114</v>
-      </c>
       <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K3" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U3" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X3" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W3" s="23" t="s">
+      <c r="Y3" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="X3" s="24" t="s">
+      <c r="Z3" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y3" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG3" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AH3" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI3" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ3" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK3" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL3" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM3" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN3" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO3" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="AO3" s="24" t="s">
-        <v>118</v>
-      </c>
       <c r="AP3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ3" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ3" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR3" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS3" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU3" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW3" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX3" s="30">
+        <v>2973000506965</v>
+      </c>
+      <c r="AY3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ3" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX3" s="30">
-        <v>2973000506951</v>
-      </c>
-      <c r="AY3" s="17" t="s">
+      <c r="BA3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ3" s="17" t="s">
+      <c r="BC3" s="31">
+        <v>93300890</v>
+      </c>
+      <c r="BD3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB3" s="29" t="s">
+      <c r="BF3" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BC3" s="31">
-        <v>93300876</v>
-      </c>
-      <c r="BD3" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE3" s="17" t="s">
+      <c r="BG3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH3" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BI3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG3" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH3" s="13" t="s">
+      <c r="BK3" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ3" s="13" t="s">
+      <c r="BM3" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK3" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL3" s="13" t="s">
+      <c r="BN3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM3" s="33" t="s">
+      <c r="BO3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP3" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN3" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP3" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ3" s="34">
         <v>99731</v>
@@ -1860,224 +1861,219 @@
       </c>
       <c r="BU3" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="G4" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>122</v>
-      </c>
       <c r="H4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K4" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P4" s="16">
         <v>1542</v>
       </c>
       <c r="Q4" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R4" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S4" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U4" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W4" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y4" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="Z4" s="24" t="s">
         <v>123</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>124</v>
       </c>
       <c r="AA4" s="25">
         <v>795</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC4" s="26">
         <v>15</v>
       </c>
       <c r="AD4" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AE4" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF4" s="35">
         <f>TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AG4" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH4" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AI4" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ4" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK4" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL4" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM4" s="22">
         <f t="shared" si="3"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AN4" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="AO4" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="AO4" s="24" t="s">
-        <v>118</v>
-      </c>
       <c r="AP4" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ4" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR4" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ4" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR4" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS4" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU4" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV4" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW4" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX4" s="30">
+        <v>2973000506966</v>
+      </c>
+      <c r="AY4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ4" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX4" s="30">
-        <v>2973000506952</v>
-      </c>
-      <c r="AY4" s="17" t="s">
+      <c r="BA4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB4" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ4" s="17" t="s">
+      <c r="BC4" s="31">
+        <v>93300891</v>
+      </c>
+      <c r="BD4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC4" s="31">
-        <v>93300877</v>
-      </c>
-      <c r="BD4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE4" s="17" t="s">
+      <c r="BF4" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF4" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH4" s="13" t="s">
+      <c r="BI4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK4" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ4" s="13" t="s">
+      <c r="BM4" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK4" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL4" s="13" t="s">
+      <c r="BN4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM4" s="33" t="s">
+      <c r="BO4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP4" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN4" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO4" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP4" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ4" s="34">
         <v>99732</v>
@@ -2093,136 +2089,131 @@
       </c>
       <c r="BU4" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV4" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="G5" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>130</v>
-      </c>
       <c r="H5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K5" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P5" s="16">
         <v>1542</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R5" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S5" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U5" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V5" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W5" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="X5" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z5" s="24" t="s">
         <v>123</v>
-      </c>
-      <c r="Y5" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z5" s="24" t="s">
-        <v>124</v>
       </c>
       <c r="AA5" s="25">
         <v>795</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC5" s="26">
         <v>20</v>
       </c>
       <c r="AD5" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AE5" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AF5" s="35">
         <f>TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AG5" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH5" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AI5" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ5" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK5" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL5" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM5" s="22">
         <f t="shared" si="3"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AN5" s="16">
         <v>92</v>
@@ -2231,86 +2222,86 @@
         <v>251</v>
       </c>
       <c r="AP5" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ5" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR5" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ5" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR5" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS5" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT5" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU5" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV5" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW5" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX5" s="30">
+        <v>2973000506967</v>
+      </c>
+      <c r="AY5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ5" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX5" s="30">
-        <v>2973000506953</v>
-      </c>
-      <c r="AY5" s="17" t="s">
+      <c r="BA5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB5" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ5" s="17" t="s">
+      <c r="BC5" s="31">
+        <v>93300892</v>
+      </c>
+      <c r="BD5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE5" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB5" s="29" t="s">
+      <c r="BF5" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BC5" s="31">
-        <v>93300878</v>
-      </c>
-      <c r="BD5" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE5" s="17" t="s">
+      <c r="BG5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH5" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF5" s="19" t="s">
+      <c r="BI5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ5" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BG5" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH5" s="13" t="s">
+      <c r="BK5" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ5" s="13" t="s">
+      <c r="BM5" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK5" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL5" s="13" t="s">
+      <c r="BN5" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM5" s="33" t="s">
+      <c r="BO5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP5" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN5" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO5" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP5" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ5" s="34">
         <v>99733</v>
@@ -2326,223 +2317,218 @@
       </c>
       <c r="BU5" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV5" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>137</v>
-      </c>
       <c r="H6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K6" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P6" s="16">
         <v>1542</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S6" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U6" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X6" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W6" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="X6" s="24" t="s">
+      <c r="Y6" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z6" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y6" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z6" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA6" s="25">
         <v>795</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC6" s="26">
         <v>40</v>
       </c>
       <c r="AD6" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF6" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE6" s="19" t="s">
+      <c r="AH6" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF6" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG6" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH6" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI6" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ6" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK6" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL6" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM6" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN6" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO6" s="24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AP6" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ6" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR6" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ6" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR6" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS6" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT6" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU6" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV6" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW6" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX6" s="30">
+        <v>2973000506968</v>
+      </c>
+      <c r="AY6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ6" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX6" s="30">
-        <v>2973000506954</v>
-      </c>
-      <c r="AY6" s="17" t="s">
+      <c r="BA6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB6" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ6" s="17" t="s">
+      <c r="BC6" s="31">
+        <v>93300893</v>
+      </c>
+      <c r="BD6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE6" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC6" s="31">
-        <v>93300879</v>
-      </c>
-      <c r="BD6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE6" s="17" t="s">
+      <c r="BF6" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF6" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH6" s="13" t="s">
+      <c r="BI6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ6" s="13" t="s">
+      <c r="BM6" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK6" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL6" s="13" t="s">
+      <c r="BN6" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM6" s="33" t="s">
+      <c r="BO6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP6" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN6" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP6" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ6" s="34">
         <v>99734</v>
@@ -2558,131 +2544,126 @@
       </c>
       <c r="BU6" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV6" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K7" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P7" s="16">
         <v>1542</v>
       </c>
       <c r="Q7" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R7" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S7" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U7" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="X7" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W7" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="X7" s="24" t="s">
+      <c r="Y7" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z7" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y7" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z7" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA7" s="25">
         <v>795</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC7" s="26">
         <v>40</v>
       </c>
       <c r="AD7" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF7" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG7" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE7" s="19" t="s">
+      <c r="AH7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF7" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG7" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH7" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI7" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ7" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK7" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL7" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM7" s="22">
         <f t="shared" si="3"/>
@@ -2695,86 +2676,86 @@
         <v>251</v>
       </c>
       <c r="AP7" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AQ7" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AS7" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT7" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU7" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV7" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW7" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX7" s="30">
+        <v>2973000506969</v>
+      </c>
+      <c r="AY7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ7" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX7" s="30">
-        <v>2973000506955</v>
-      </c>
-      <c r="AY7" s="17" t="s">
+      <c r="BA7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB7" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ7" s="17" t="s">
+      <c r="BC7" s="31">
+        <v>93300894</v>
+      </c>
+      <c r="BD7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE7" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC7" s="31">
-        <v>93300880</v>
-      </c>
-      <c r="BD7" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE7" s="17" t="s">
+      <c r="BF7" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH7" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF7" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG7" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH7" s="13" t="s">
+      <c r="BI7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK7" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ7" s="13" t="s">
+      <c r="BM7" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK7" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL7" s="13" t="s">
+      <c r="BN7" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM7" s="33" t="s">
+      <c r="BO7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP7" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN7" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP7" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ7" s="34">
         <v>99735</v>
@@ -2790,136 +2771,136 @@
       </c>
       <c r="BU7" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV7" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K8" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P8" s="16">
         <v>1542</v>
       </c>
       <c r="Q8" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R8" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S8" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U8" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V8" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="X8" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Z8" s="24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AA8" s="25">
         <v>795</v>
       </c>
       <c r="AB8" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC8" s="26">
         <v>40</v>
       </c>
       <c r="AD8" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AE8" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF8" s="35">
         <f>TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH8" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AI8" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ8" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK8" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL8" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM8" s="22">
         <f t="shared" si="3"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AN8" s="16">
         <v>92</v>
@@ -2928,86 +2909,86 @@
         <v>251</v>
       </c>
       <c r="AP8" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AQ8" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AR8" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AS8" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT8" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU8" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV8" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW8" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX8" s="30">
+        <v>2973000506970</v>
+      </c>
+      <c r="AY8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ8" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX8" s="30">
-        <v>2973000506956</v>
-      </c>
-      <c r="AY8" s="17" t="s">
+      <c r="BA8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB8" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ8" s="17" t="s">
+      <c r="BC8" s="31">
+        <v>93300895</v>
+      </c>
+      <c r="BD8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE8" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC8" s="31">
-        <v>93300881</v>
-      </c>
-      <c r="BD8" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE8" s="17" t="s">
+      <c r="BF8" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH8" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF8" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG8" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH8" s="13" t="s">
+      <c r="BI8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ8" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK8" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL8" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ8" s="13" t="s">
+      <c r="BM8" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK8" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL8" s="13" t="s">
+      <c r="BN8" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM8" s="33" t="s">
+      <c r="BO8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP8" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN8" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP8" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ8" s="34">
         <v>99736</v>
@@ -3023,131 +3004,131 @@
       </c>
       <c r="BU8" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV8" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K9" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P9" s="16">
         <v>1542</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U9" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="X9" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W9" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="X9" s="24" t="s">
-        <v>86</v>
-      </c>
       <c r="Y9" s="24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Z9" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA9" s="25">
         <v>795</v>
       </c>
       <c r="AB9" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC9" s="26">
         <v>20</v>
       </c>
       <c r="AD9" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE9" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF9" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG9" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE9" s="19" t="s">
+      <c r="AH9" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF9" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG9" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH9" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI9" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ9" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK9" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL9" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM9" s="22">
         <f t="shared" si="3"/>
@@ -3160,86 +3141,86 @@
         <v>251</v>
       </c>
       <c r="AP9" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AQ9" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AS9" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT9" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU9" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW9" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX9" s="30">
+        <v>2973000506971</v>
+      </c>
+      <c r="AY9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ9" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX9" s="30">
-        <v>2973000506957</v>
-      </c>
-      <c r="AY9" s="17" t="s">
+      <c r="BA9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB9" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ9" s="17" t="s">
+      <c r="BC9" s="31">
+        <v>93300896</v>
+      </c>
+      <c r="BD9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE9" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC9" s="31">
-        <v>93300882</v>
-      </c>
-      <c r="BD9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE9" s="17" t="s">
+      <c r="BF9" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH9" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF9" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG9" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH9" s="13" t="s">
+      <c r="BI9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ9" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK9" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL9" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ9" s="13" t="s">
+      <c r="BM9" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK9" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL9" s="13" t="s">
+      <c r="BN9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM9" s="33" t="s">
+      <c r="BO9" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP9" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN9" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP9" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ9" s="34">
         <v>99737</v>
@@ -3255,131 +3236,131 @@
       </c>
       <c r="BU9" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K10" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P10" s="16">
         <v>1542</v>
       </c>
       <c r="Q10" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R10" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S10" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U10" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V10" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="X10" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W10" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="X10" s="24" t="s">
+      <c r="Y10" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z10" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y10" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="Z10" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA10" s="25">
         <v>795</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC10" s="26">
         <v>40</v>
       </c>
       <c r="AD10" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF10" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG10" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE10" s="19" t="s">
+      <c r="AH10" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF10" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG10" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH10" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI10" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ10" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK10" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL10" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM10" s="22">
         <f t="shared" si="3"/>
@@ -3392,86 +3373,86 @@
         <v>251</v>
       </c>
       <c r="AP10" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AQ10" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="AR10" s="19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="AS10" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT10" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU10" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV10" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW10" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX10" s="30">
+        <v>2973000506972</v>
+      </c>
+      <c r="AY10" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX10" s="30">
-        <v>2973000506958</v>
-      </c>
-      <c r="AY10" s="17" t="s">
+      <c r="BA10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB10" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ10" s="17" t="s">
+      <c r="BC10" s="31">
+        <v>93300897</v>
+      </c>
+      <c r="BD10" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE10" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC10" s="31">
-        <v>93300883</v>
-      </c>
-      <c r="BD10" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE10" s="17" t="s">
+      <c r="BF10" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG10" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH10" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF10" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG10" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH10" s="13" t="s">
+      <c r="BI10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ10" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK10" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL10" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ10" s="13" t="s">
+      <c r="BM10" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK10" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL10" s="13" t="s">
+      <c r="BN10" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM10" s="33" t="s">
+      <c r="BO10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP10" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN10" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP10" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ10" s="34">
         <v>99738</v>
@@ -3487,218 +3468,218 @@
       </c>
       <c r="BU10" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV10" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K11" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P11" s="16">
         <v>1542</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R11" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S11" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U11" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V11" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W11" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W11" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="X11" s="24" t="s">
+      <c r="Y11" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z11" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y11" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z11" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA11" s="25">
         <v>795</v>
       </c>
       <c r="AB11" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC11" s="26">
         <v>40</v>
       </c>
       <c r="AD11" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE11" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF11" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG11" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE11" s="19" t="s">
+      <c r="AH11" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF11" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG11" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH11" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI11" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ11" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK11" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL11" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM11" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN11" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO11" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AP11" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ11" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR11" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ11" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS11" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT11" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU11" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV11" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW11" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX11" s="30">
+        <v>2973000506973</v>
+      </c>
+      <c r="AY11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ11" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX11" s="30">
-        <v>2973000506959</v>
-      </c>
-      <c r="AY11" s="17" t="s">
+      <c r="BA11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB11" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ11" s="17" t="s">
+      <c r="BC11" s="31">
+        <v>93300898</v>
+      </c>
+      <c r="BD11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE11" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC11" s="31">
-        <v>93300884</v>
-      </c>
-      <c r="BD11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE11" s="17" t="s">
+      <c r="BF11" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH11" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF11" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH11" s="13" t="s">
+      <c r="BI11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ11" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK11" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL11" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ11" s="13" t="s">
+      <c r="BM11" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK11" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL11" s="13" t="s">
+      <c r="BN11" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM11" s="33" t="s">
+      <c r="BO11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP11" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN11" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP11" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ11" s="34">
         <v>99739</v>
@@ -3714,214 +3695,214 @@
       </c>
       <c r="BU11" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV11" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K12" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P12" s="16">
         <v>1542</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R12" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S12" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U12" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V12" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W12" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W12" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>86</v>
-      </c>
       <c r="Y12" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Z12" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA12" s="25">
         <v>795</v>
       </c>
       <c r="AB12" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC12" s="26">
         <v>30</v>
       </c>
       <c r="AD12" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF12" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG12" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE12" s="19" t="s">
+      <c r="AH12" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF12" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG12" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH12" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI12" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ12" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK12" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL12" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM12" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN12" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AP12" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ12" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR12" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ12" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="AR12" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS12" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT12" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU12" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV12" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW12" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX12" s="30">
+        <v>2973000506974</v>
+      </c>
+      <c r="AY12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX12" s="30">
-        <v>2973000506960</v>
-      </c>
-      <c r="AY12" s="17" t="s">
+      <c r="BA12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB12" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ12" s="17" t="s">
+      <c r="BC12" s="31">
+        <v>93300899</v>
+      </c>
+      <c r="BD12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE12" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC12" s="31">
-        <v>93300885</v>
-      </c>
-      <c r="BD12" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE12" s="17" t="s">
+      <c r="BF12" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH12" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF12" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG12" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH12" s="13" t="s">
+      <c r="BI12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ12" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK12" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL12" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ12" s="13" t="s">
+      <c r="BM12" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK12" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL12" s="13" t="s">
+      <c r="BN12" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM12" s="33" t="s">
+      <c r="BO12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP12" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN12" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP12" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ12" s="34">
         <v>99740</v>
@@ -3937,215 +3918,215 @@
       </c>
       <c r="BU12" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV12" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K13" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O13" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P13" s="16">
         <v>1542</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R13" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S13" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U13" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V13" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W13" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X13" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y13" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z13" s="24" t="s">
         <v>123</v>
-      </c>
-      <c r="Y13" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z13" s="24" t="s">
-        <v>124</v>
       </c>
       <c r="AA13" s="25">
         <v>795</v>
       </c>
       <c r="AB13" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC13" s="26">
         <v>25</v>
       </c>
       <c r="AD13" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AE13" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF13" s="35">
         <f>TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AG13" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH13" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AI13" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ13" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK13" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL13" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM13" s="22">
         <f t="shared" si="3"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AN13" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO13" s="24" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AP13" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ13" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR13" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ13" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR13" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS13" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT13" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU13" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV13" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW13" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX13" s="30">
+        <v>2973000506975</v>
+      </c>
+      <c r="AY13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX13" s="30">
-        <v>2973000506961</v>
-      </c>
-      <c r="AY13" s="17" t="s">
+      <c r="BA13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB13" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ13" s="17" t="s">
+      <c r="BC13" s="31">
+        <v>93300900</v>
+      </c>
+      <c r="BD13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC13" s="31">
-        <v>93300886</v>
-      </c>
-      <c r="BD13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE13" s="17" t="s">
+      <c r="BF13" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH13" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF13" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH13" s="13" t="s">
+      <c r="BI13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK13" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL13" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ13" s="13" t="s">
+      <c r="BM13" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK13" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL13" s="13" t="s">
+      <c r="BN13" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM13" s="33" t="s">
+      <c r="BO13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP13" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN13" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP13" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ13" s="34">
         <v>99741</v>
@@ -4161,215 +4142,215 @@
       </c>
       <c r="BU13" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV13" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K14" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O14" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P14" s="16">
         <v>1542</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R14" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S14" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T14" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U14" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="W14" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X14" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AA14" s="25">
         <v>795</v>
       </c>
       <c r="AB14" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC14" s="26">
         <v>40</v>
       </c>
       <c r="AD14" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AE14" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AF14" s="35">
         <f>TODAY()+365</f>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AG14" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH14" s="16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AI14" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ14" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK14" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL14" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM14" s="22">
         <f t="shared" si="3"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="AN14" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO14" s="24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AP14" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ14" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR14" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ14" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR14" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS14" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT14" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU14" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV14" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW14" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX14" s="30">
+        <v>2973000506976</v>
+      </c>
+      <c r="AY14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ14" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX14" s="30">
-        <v>2973000506962</v>
-      </c>
-      <c r="AY14" s="17" t="s">
+      <c r="BA14" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB14" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ14" s="17" t="s">
+      <c r="BC14" s="31">
+        <v>93300901</v>
+      </c>
+      <c r="BD14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA14" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC14" s="31">
-        <v>93300887</v>
-      </c>
-      <c r="BD14" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE14" s="17" t="s">
+      <c r="BF14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH14" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF14" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG14" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH14" s="13" t="s">
+      <c r="BI14" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ14" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK14" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL14" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI14" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ14" s="13" t="s">
+      <c r="BM14" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK14" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL14" s="13" t="s">
+      <c r="BN14" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM14" s="33" t="s">
+      <c r="BO14" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP14" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN14" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO14" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP14" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ14" s="34">
         <v>99742</v>
@@ -4385,214 +4366,223 @@
       </c>
       <c r="BU14" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV14" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="11"/>
+        <v>175</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="D15" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>178</v>
+      </c>
       <c r="H15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K15" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O15" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P15" s="16">
         <v>1542</v>
       </c>
       <c r="Q15" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R15" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S15" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U15" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V15" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W15" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X15" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W15" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="X15" s="24" t="s">
-        <v>86</v>
-      </c>
       <c r="Y15" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z15" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA15" s="25">
         <v>795</v>
       </c>
       <c r="AB15" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC15" s="26">
         <v>25</v>
       </c>
       <c r="AD15" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE15" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF15" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG15" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE15" s="19" t="s">
+      <c r="AH15" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF15" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG15" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH15" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI15" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ15" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK15" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL15" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM15" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN15" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO15" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AP15" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ15" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR15" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ15" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR15" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS15" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT15" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU15" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV15" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW15" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX15" s="30">
+        <v>2973000506977</v>
+      </c>
+      <c r="AY15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ15" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX15" s="30">
-        <v>2973000506963</v>
-      </c>
-      <c r="AY15" s="17" t="s">
+      <c r="BA15" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB15" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ15" s="17" t="s">
+      <c r="BC15" s="31">
+        <v>93300902</v>
+      </c>
+      <c r="BD15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE15" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA15" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC15" s="31">
-        <v>93300888</v>
-      </c>
-      <c r="BD15" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE15" s="17" t="s">
+      <c r="BF15" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH15" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF15" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG15" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH15" s="13" t="s">
+      <c r="BI15" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK15" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL15" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI15" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ15" s="13" t="s">
+      <c r="BM15" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK15" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL15" s="13" t="s">
+      <c r="BN15" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM15" s="33" t="s">
+      <c r="BO15" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP15" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN15" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO15" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP15" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ15" s="34">
         <v>99743</v>
@@ -4608,214 +4598,223 @@
       </c>
       <c r="BU15" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV15" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C16" s="11"/>
+      <c r="C16" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="D16" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="H16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="16" t="s">
         <v>77</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="K16" s="17">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45727</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O16" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P16" s="16">
         <v>1542</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R16" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S16" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U16" s="22">
         <f t="shared" si="1"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="V16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="W16" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="X16" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="W16" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="X16" s="24" t="s">
+      <c r="Y16" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z16" s="24" t="s">
         <v>86</v>
-      </c>
-      <c r="Y16" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z16" s="24" t="s">
-        <v>88</v>
       </c>
       <c r="AA16" s="25">
         <v>795</v>
       </c>
       <c r="AB16" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC16" s="26">
         <v>40</v>
       </c>
       <c r="AD16" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE16" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF16" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG16" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="AE16" s="19" t="s">
+      <c r="AH16" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AF16" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG16" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH16" s="16" t="s">
-        <v>93</v>
-      </c>
       <c r="AI16" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AJ16" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AK16" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AL16" s="17">
         <f t="shared" si="2"/>
-        <v>45699</v>
+        <v>45703</v>
       </c>
       <c r="AM16" s="22">
         <f t="shared" si="3"/>
         <v>NaN</v>
       </c>
       <c r="AN16" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AO16" s="24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AP16" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ16" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="AR16" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="AQ16" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="AR16" s="19" t="s">
-        <v>96</v>
-      </c>
       <c r="AS16" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AT16" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AU16" s="17">
         <f t="shared" si="4"/>
-        <v>45737</v>
+        <v>45741</v>
       </c>
       <c r="AV16" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AW16" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX16" s="30">
+        <v>2973000506978</v>
+      </c>
+      <c r="AY16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ16" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AX16" s="30">
-        <v>2973000506964</v>
-      </c>
-      <c r="AY16" s="17" t="s">
+      <c r="BA16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB16" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="AZ16" s="17" t="s">
+      <c r="BC16" s="31">
+        <v>93300903</v>
+      </c>
+      <c r="BD16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="BA16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="BC16" s="31">
-        <v>93300889</v>
-      </c>
-      <c r="BD16" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BE16" s="17" t="s">
+      <c r="BF16" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH16" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="BF16" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="BG16" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH16" s="13" t="s">
+      <c r="BI16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BJ16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK16" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL16" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BI16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ16" s="13" t="s">
+      <c r="BM16" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BK16" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL16" s="13" t="s">
+      <c r="BN16" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BM16" s="33" t="s">
+      <c r="BO16" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BP16" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="BN16" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO16" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP16" s="13" t="s">
-        <v>108</v>
       </c>
       <c r="BQ16" s="34">
         <v>99744</v>
@@ -4831,10 +4830,10 @@
       </c>
       <c r="BU16" s="22">
         <f t="shared" si="5"/>
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="BV16" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/TestDataSloveniaMKv1.xlsx
+++ b/Data/Hires/TestDataSloveniaMKv1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="191">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,16 +229,25 @@
     <t>Test1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Cordie Bradtke' Employee:{undefined}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Collective Agreement', { exact: true })[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>795 Store Management (Zogop Dogegy (10185858))</t>
   </si>
   <si>
     <t>Slovenia</t>
   </si>
   <si>
-    <t>Jeffrey</t>
-  </si>
-  <si>
-    <t>Crona</t>
+    <t>Kelsie</t>
+  </si>
+  <si>
+    <t>Beatty</t>
   </si>
   <si>
     <t xml:space="preserve">070-417-626 </t>
@@ -265,7 +274,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 72978257</t>
+    <t>Auto 21947801</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -343,26 +352,405 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Liana Hodkiewicz' Employee:{undefined}Error: [31mTimed out 5000ms waiting for [39m[2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m()[22m
-Locator: locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')
-Expected: visible
-Received: &lt;element(s) not found&gt;
+    <t xml:space="preserve">Test failed for 'Gillian Bruen' Employee:{10697916}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- expect.toBeVisible with timeout 5000ms[22m
-[2m  - waiting for locator('xpath=((//div[contains(text(),\'Awaiting Action\')]//ancestor::td//following-sibling::td)[3])[1]')[22m
+  [2m- waiting for locator('//div[@data-automation-id=\'titleText\'][contains(./text(),\'Personal Information Change: Gillian Bruen\')]')[22m
+[2m  -   locator resolved to &lt;div class="css-t9tuu3" data-automation-id="titleText"&gt;Personal Information Change: Gillian Bruen (10697…&lt;/div&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
 </t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>795 Recruitment (Zosig Depazi (10280602))</t>
   </si>
   <si>
-    <t>Stacey</t>
-  </si>
-  <si>
-    <t>Runolfsdottir</t>
+    <t>Gillian</t>
+  </si>
+  <si>
+    <t>Bruen</t>
   </si>
   <si>
     <t>No</t>
@@ -380,13 +768,18 @@
     <t>Test3</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Lester Ferry' Employee:{10697917}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+Expected: [32m"undefined"[39m
+Received: [31m"SVN Monthly"[39m</t>
+  </si>
+  <si>
     <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
   </si>
   <si>
-    <t>Karine</t>
-  </si>
-  <si>
-    <t>Ruecker</t>
+    <t>Lester</t>
+  </si>
+  <si>
+    <t>Ferry</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -404,13 +797,19 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>Sincere</t>
-  </si>
-  <si>
-    <t>Gusikowski</t>
-  </si>
-  <si>
-    <t>Auto 34001849</t>
+    <t>10697918</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Reagan</t>
+  </si>
+  <si>
+    <t>Hilpert</t>
+  </si>
+  <si>
+    <t>Auto 17527611</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -684,7 +1083,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1411,105 +1810,109 @@
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
+      <c r="B2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D2" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K2" s="17">
         <f t="shared" ref="K2:K16" si="0">TODAY()-7</f>
         <v>45727</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2" s="16">
         <v>1542</v>
       </c>
       <c r="Q2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S2" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="22">
         <f t="shared" ref="U2:U16" si="1">TODAY()-31</f>
         <v>45703</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W2" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="X2" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA2" s="25">
         <v>795</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC2" s="26">
         <v>40</v>
       </c>
       <c r="AD2" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE2" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG2" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH2" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI2" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ2" s="17">
         <f t="shared" ref="AJ2:AL16" si="2">TODAY()-31</f>
@@ -1534,86 +1937,86 @@
         <v>251</v>
       </c>
       <c r="AP2" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ2" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT2" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU2" s="17">
         <f t="shared" ref="AU2:AU16" si="4">TODAY()+7</f>
         <v>45741</v>
       </c>
       <c r="AV2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW2" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX2" s="30">
         <v>2973000506964</v>
       </c>
       <c r="AY2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB2" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC2" s="31">
         <v>93300889</v>
       </c>
       <c r="BD2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE2" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF2" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BG2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH2" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ2" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL2" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM2" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN2" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO2" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP2" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ2" s="34">
         <v>99730</v>
@@ -1632,116 +2035,116 @@
         <v>46099</v>
       </c>
       <c r="BV2" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K3" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P3" s="16">
         <v>1542</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X3" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z3" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA3" s="25">
         <v>795</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC3" s="26">
         <v>40</v>
       </c>
       <c r="AD3" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE3" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF3" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH3" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI3" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ3" s="17">
         <f t="shared" si="2"/>
@@ -1760,92 +2163,92 @@
         <v>NaN</v>
       </c>
       <c r="AN3" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AP3" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ3" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR3" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT3" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU3" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW3" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX3" s="30">
         <v>2973000506965</v>
       </c>
       <c r="AY3" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ3" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB3" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC3" s="31">
         <v>93300890</v>
       </c>
       <c r="BD3" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE3" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF3" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BG3" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH3" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ3" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK3" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL3" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM3" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN3" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO3" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP3" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ3" s="34">
         <v>99731</v>
@@ -1864,112 +2267,117 @@
         <v>46099</v>
       </c>
       <c r="BV3" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="11"/>
+        <v>119</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D4" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K4" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P4" s="16">
         <v>1542</v>
       </c>
       <c r="Q4" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R4" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S4" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U4" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W4" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X4" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z4" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA4" s="25">
         <v>795</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC4" s="26">
         <v>15</v>
       </c>
       <c r="AD4" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE4" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AF4" s="35">
         <f>TODAY()+365</f>
         <v>46099</v>
       </c>
       <c r="AG4" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH4" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI4" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ4" s="17">
         <f t="shared" si="2"/>
@@ -1988,92 +2396,92 @@
         <v>46099</v>
       </c>
       <c r="AN4" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO4" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AP4" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ4" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR4" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS4" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT4" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU4" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW4" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX4" s="30">
         <v>2973000506966</v>
       </c>
       <c r="AY4" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ4" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB4" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC4" s="31">
         <v>93300891</v>
       </c>
       <c r="BD4" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE4" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF4" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG4" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH4" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ4" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK4" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL4" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM4" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN4" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO4" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP4" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ4" s="34">
         <v>99732</v>
@@ -2092,112 +2500,117 @@
         <v>46099</v>
       </c>
       <c r="BV4" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="D5" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K5" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P5" s="16">
         <v>1542</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R5" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S5" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U5" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V5" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W5" s="23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="X5" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y5" s="24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA5" s="25">
         <v>795</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC5" s="26">
         <v>20</v>
       </c>
       <c r="AD5" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE5" s="19" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AF5" s="35">
         <f>TODAY()+365</f>
         <v>46099</v>
       </c>
       <c r="AG5" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH5" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI5" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ5" s="17">
         <f t="shared" si="2"/>
@@ -2222,86 +2635,86 @@
         <v>251</v>
       </c>
       <c r="AP5" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ5" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR5" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS5" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT5" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU5" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW5" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX5" s="30">
         <v>2973000506967</v>
       </c>
       <c r="AY5" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ5" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB5" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC5" s="31">
         <v>93300892</v>
       </c>
       <c r="BD5" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE5" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF5" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BG5" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH5" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ5" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK5" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL5" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM5" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN5" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO5" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP5" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ5" s="34">
         <v>99733</v>
@@ -2320,111 +2733,111 @@
         <v>46099</v>
       </c>
       <c r="BV5" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K6" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P6" s="16">
         <v>1542</v>
       </c>
       <c r="Q6" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S6" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U6" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V6" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W6" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X6" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="24" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Z6" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA6" s="25">
         <v>795</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC6" s="26">
         <v>40</v>
       </c>
       <c r="AD6" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE6" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF6" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG6" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH6" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI6" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ6" s="17">
         <f t="shared" si="2"/>
@@ -2443,92 +2856,92 @@
         <v>NaN</v>
       </c>
       <c r="AN6" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO6" s="24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AP6" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ6" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR6" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS6" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT6" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU6" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW6" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX6" s="30">
         <v>2973000506968</v>
       </c>
       <c r="AY6" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ6" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB6" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC6" s="31">
         <v>93300893</v>
       </c>
       <c r="BD6" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE6" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF6" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG6" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH6" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ6" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK6" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL6" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM6" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN6" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO6" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP6" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ6" s="34">
         <v>99734</v>
@@ -2547,111 +2960,111 @@
         <v>46099</v>
       </c>
       <c r="BV6" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P7" s="16">
         <v>1542</v>
       </c>
       <c r="Q7" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R7" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S7" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U7" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V7" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="X7" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y7" s="24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Z7" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA7" s="25">
         <v>795</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC7" s="26">
         <v>40</v>
       </c>
       <c r="AD7" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE7" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF7" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG7" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH7" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI7" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ7" s="17">
         <f t="shared" si="2"/>
@@ -2676,86 +3089,86 @@
         <v>251</v>
       </c>
       <c r="AP7" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ7" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AS7" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT7" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU7" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW7" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX7" s="30">
         <v>2973000506969</v>
       </c>
       <c r="AY7" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ7" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB7" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC7" s="31">
         <v>93300894</v>
       </c>
       <c r="BD7" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE7" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF7" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG7" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH7" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ7" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK7" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL7" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM7" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN7" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO7" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP7" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ7" s="34">
         <v>99735</v>
@@ -2774,117 +3187,117 @@
         <v>46099</v>
       </c>
       <c r="BV7" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K8" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M8" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O8" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P8" s="16">
         <v>1542</v>
       </c>
       <c r="Q8" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R8" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S8" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U8" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V8" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W8" s="23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="X8" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y8" s="24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Z8" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA8" s="25">
         <v>795</v>
       </c>
       <c r="AB8" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC8" s="26">
         <v>40</v>
       </c>
       <c r="AD8" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE8" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF8" s="35">
         <f>TODAY()+365</f>
         <v>46099</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH8" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI8" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ8" s="17">
         <f t="shared" si="2"/>
@@ -2909,86 +3322,86 @@
         <v>251</v>
       </c>
       <c r="AP8" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ8" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AR8" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AS8" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT8" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU8" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW8" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX8" s="30">
         <v>2973000506970</v>
       </c>
       <c r="AY8" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ8" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB8" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC8" s="31">
         <v>93300895</v>
       </c>
       <c r="BD8" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE8" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF8" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG8" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH8" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ8" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK8" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL8" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM8" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN8" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO8" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP8" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ8" s="34">
         <v>99736</v>
@@ -3007,116 +3420,116 @@
         <v>46099</v>
       </c>
       <c r="BV8" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K9" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P9" s="16">
         <v>1542</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U9" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V9" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W9" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="X9" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y9" s="24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Z9" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA9" s="25">
         <v>795</v>
       </c>
       <c r="AB9" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC9" s="26">
         <v>20</v>
       </c>
       <c r="AD9" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE9" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF9" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG9" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH9" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI9" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ9" s="17">
         <f t="shared" si="2"/>
@@ -3141,86 +3554,86 @@
         <v>251</v>
       </c>
       <c r="AP9" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ9" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AS9" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT9" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU9" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW9" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX9" s="30">
         <v>2973000506971</v>
       </c>
       <c r="AY9" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ9" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB9" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC9" s="31">
         <v>93300896</v>
       </c>
       <c r="BD9" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE9" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF9" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG9" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH9" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ9" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK9" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL9" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM9" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN9" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO9" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP9" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ9" s="34">
         <v>99737</v>
@@ -3239,116 +3652,116 @@
         <v>46099</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K10" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M10" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P10" s="16">
         <v>1542</v>
       </c>
       <c r="Q10" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R10" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S10" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U10" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V10" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="X10" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y10" s="24" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Z10" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA10" s="25">
         <v>795</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC10" s="26">
         <v>40</v>
       </c>
       <c r="AD10" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE10" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF10" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG10" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH10" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI10" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ10" s="17">
         <f t="shared" si="2"/>
@@ -3373,86 +3786,86 @@
         <v>251</v>
       </c>
       <c r="AP10" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ10" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AR10" s="19" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AS10" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT10" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU10" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW10" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX10" s="30">
         <v>2973000506972</v>
       </c>
       <c r="AY10" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ10" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB10" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC10" s="31">
         <v>93300897</v>
       </c>
       <c r="BD10" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE10" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF10" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG10" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH10" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ10" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK10" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL10" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM10" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN10" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO10" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP10" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ10" s="34">
         <v>99738</v>
@@ -3471,111 +3884,111 @@
         <v>46099</v>
       </c>
       <c r="BV10" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K11" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O11" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P11" s="16">
         <v>1542</v>
       </c>
       <c r="Q11" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R11" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S11" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U11" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V11" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W11" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X11" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y11" s="24" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Z11" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA11" s="25">
         <v>795</v>
       </c>
       <c r="AB11" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC11" s="26">
         <v>40</v>
       </c>
       <c r="AD11" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE11" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF11" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG11" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH11" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI11" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ11" s="17">
         <f t="shared" si="2"/>
@@ -3594,92 +4007,92 @@
         <v>NaN</v>
       </c>
       <c r="AN11" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO11" s="24" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AP11" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ11" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AR11" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS11" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT11" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU11" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW11" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX11" s="30">
         <v>2973000506973</v>
       </c>
       <c r="AY11" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ11" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB11" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC11" s="31">
         <v>93300898</v>
       </c>
       <c r="BD11" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE11" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF11" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG11" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH11" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ11" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK11" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL11" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM11" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN11" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO11" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP11" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ11" s="34">
         <v>99739</v>
@@ -3698,107 +4111,107 @@
         <v>46099</v>
       </c>
       <c r="BV11" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K12" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P12" s="16">
         <v>1542</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R12" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S12" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U12" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V12" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W12" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X12" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Z12" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA12" s="25">
         <v>795</v>
       </c>
       <c r="AB12" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC12" s="26">
         <v>30</v>
       </c>
       <c r="AD12" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE12" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF12" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG12" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH12" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI12" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ12" s="17">
         <f t="shared" si="2"/>
@@ -3817,92 +4230,92 @@
         <v>NaN</v>
       </c>
       <c r="AN12" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AP12" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ12" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AR12" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS12" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT12" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU12" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW12" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX12" s="30">
         <v>2973000506974</v>
       </c>
       <c r="AY12" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ12" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB12" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC12" s="31">
         <v>93300899</v>
       </c>
       <c r="BD12" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE12" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF12" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG12" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH12" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ12" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK12" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL12" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM12" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN12" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO12" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP12" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ12" s="34">
         <v>99740</v>
@@ -3921,108 +4334,108 @@
         <v>46099</v>
       </c>
       <c r="BV12" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K13" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O13" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P13" s="16">
         <v>1542</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R13" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S13" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U13" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V13" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W13" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X13" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y13" s="24" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Z13" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA13" s="25">
         <v>795</v>
       </c>
       <c r="AB13" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC13" s="26">
         <v>25</v>
       </c>
       <c r="AD13" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE13" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF13" s="35">
         <f>TODAY()+365</f>
         <v>46099</v>
       </c>
       <c r="AG13" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH13" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI13" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ13" s="17">
         <f t="shared" si="2"/>
@@ -4041,92 +4454,92 @@
         <v>46099</v>
       </c>
       <c r="AN13" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO13" s="24" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="AP13" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ13" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR13" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS13" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT13" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU13" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW13" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX13" s="30">
         <v>2973000506975</v>
       </c>
       <c r="AY13" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ13" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB13" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC13" s="31">
         <v>93300900</v>
       </c>
       <c r="BD13" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE13" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF13" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG13" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH13" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ13" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK13" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL13" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM13" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN13" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO13" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP13" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ13" s="34">
         <v>99741</v>
@@ -4145,108 +4558,108 @@
         <v>46099</v>
       </c>
       <c r="BV13" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K14" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N14" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O14" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P14" s="16">
         <v>1542</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R14" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S14" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T14" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U14" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W14" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X14" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="25">
         <v>795</v>
       </c>
       <c r="AB14" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC14" s="26">
         <v>40</v>
       </c>
       <c r="AD14" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE14" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF14" s="35">
         <f>TODAY()+365</f>
         <v>46099</v>
       </c>
       <c r="AG14" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH14" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI14" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ14" s="17">
         <f t="shared" si="2"/>
@@ -4265,92 +4678,92 @@
         <v>46099</v>
       </c>
       <c r="AN14" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO14" s="24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AP14" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ14" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR14" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS14" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT14" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU14" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW14" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX14" s="30">
         <v>2973000506976</v>
       </c>
       <c r="AY14" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ14" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB14" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC14" s="31">
         <v>93300901</v>
       </c>
       <c r="BD14" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE14" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF14" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG14" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH14" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ14" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK14" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL14" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM14" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN14" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO14" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP14" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ14" s="34">
         <v>99742</v>
@@ -4369,116 +4782,116 @@
         <v>46099</v>
       </c>
       <c r="BV14" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K15" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M15" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O15" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P15" s="16">
         <v>1542</v>
       </c>
       <c r="Q15" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R15" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S15" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U15" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W15" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X15" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y15" s="24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Z15" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AA15" s="25">
         <v>795</v>
       </c>
       <c r="AB15" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC15" s="26">
         <v>25</v>
       </c>
       <c r="AD15" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE15" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF15" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG15" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH15" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI15" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ15" s="17">
         <f t="shared" si="2"/>
@@ -4497,92 +4910,92 @@
         <v>NaN</v>
       </c>
       <c r="AN15" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO15" s="24" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AP15" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ15" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AR15" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS15" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT15" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU15" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW15" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX15" s="30">
         <v>2973000506977</v>
       </c>
       <c r="AY15" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ15" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB15" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC15" s="31">
         <v>93300902</v>
       </c>
       <c r="BD15" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE15" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF15" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG15" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH15" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ15" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK15" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL15" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM15" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN15" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO15" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP15" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ15" s="34">
         <v>99743</v>
@@ -4601,116 +5014,116 @@
         <v>46099</v>
       </c>
       <c r="BV15" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K16" s="17">
         <f t="shared" si="0"/>
         <v>45727</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M16" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O16" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P16" s="16">
         <v>1542</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R16" s="20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S16" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U16" s="22">
         <f t="shared" si="1"/>
         <v>45703</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W16" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X16" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y16" s="24" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Z16" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA16" s="25">
         <v>795</v>
       </c>
       <c r="AB16" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AC16" s="26">
         <v>40</v>
       </c>
       <c r="AD16" s="27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AE16" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AF16" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG16" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH16" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI16" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AJ16" s="17">
         <f t="shared" si="2"/>
@@ -4729,92 +5142,92 @@
         <v>NaN</v>
       </c>
       <c r="AN16" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AO16" s="24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AP16" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AQ16" s="24" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AR16" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS16" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AT16" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AU16" s="17">
         <f t="shared" si="4"/>
         <v>45741</v>
       </c>
       <c r="AV16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AW16" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AX16" s="30">
         <v>2973000506978</v>
       </c>
       <c r="AY16" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AZ16" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BA16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BB16" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BC16" s="31">
         <v>93300903</v>
       </c>
       <c r="BD16" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BE16" s="17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BF16" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BG16" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BH16" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BI16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BJ16" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BK16" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="BL16" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BM16" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BN16" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BO16" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BP16" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BQ16" s="34">
         <v>99744</v>
@@ -4833,7 +5246,7 @@
         <v>46099</v>
       </c>
       <c r="BV16" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/TestDataSloveniaMKv1.xlsx
+++ b/Data/Hires/TestDataSloveniaMKv1.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{3BDC4FFC-8847-4F75-A8A0-26E78603E1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="203">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,725 +244,364 @@
     <t>Test1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Cordie Bradtke' Employee:{undefined}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+    <t>10698062</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>795 Store Management (Zogop Dogegy (10185858))</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Halvorson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070-417-626 </t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Ljubljana</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@email.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>Auto 95021107</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>5 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
+  </si>
+  <si>
+    <t>Asistent v prodaji</t>
+  </si>
+  <si>
+    <t>IV.</t>
+  </si>
+  <si>
+    <t>Unique Master Citizen Number</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>01/01/2045</t>
+  </si>
+  <si>
+    <t>Slovenia Tax Number</t>
+  </si>
+  <si>
+    <t>01/01/2041</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Citizen (Slovenia)</t>
+  </si>
+  <si>
+    <t>TestBankOFSlovenia</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>SI56 2633 0001 2039 086</t>
+  </si>
+  <si>
+    <t>Grun Frun</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>SVN Monthly</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>10698063</t>
+  </si>
+  <si>
+    <t>795 Recruitment (Zosig Depazi (10280602))</t>
+  </si>
+  <si>
+    <t>Mittie</t>
+  </si>
+  <si>
+    <t>Tillman</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>10698065</t>
+  </si>
+  <si>
+    <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
+  </si>
+  <si>
+    <t>Aurore</t>
+  </si>
+  <si>
+    <t>Kreiger</t>
+  </si>
+  <si>
+    <t>Fixed Term (Fixed Term)</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>3 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>10698066</t>
+  </si>
+  <si>
+    <t>Antwon</t>
+  </si>
+  <si>
+    <t>Johns</t>
+  </si>
+  <si>
+    <t>Auto 5780199</t>
+  </si>
+  <si>
+    <t>Team Manager - Retail_NEW</t>
+  </si>
+  <si>
+    <t>4 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>10698068</t>
+  </si>
+  <si>
+    <t>Rebeka</t>
+  </si>
+  <si>
+    <t>Watsica</t>
+  </si>
+  <si>
+    <t>In-Store Visual Merchandising Assistant_NEW</t>
+  </si>
+  <si>
+    <t>256 Visual Merchandising</t>
+  </si>
+  <si>
+    <t>Test6</t>
+  </si>
+  <si>
+    <t>10698070</t>
+  </si>
+  <si>
+    <t>Aron</t>
+  </si>
+  <si>
+    <t>Armstrong-McKenzie</t>
+  </si>
+  <si>
+    <t>Auto 7225502</t>
+  </si>
+  <si>
+    <t>Strokovni sodelavec v kadrovski službi</t>
+  </si>
+  <si>
+    <t>V.</t>
+  </si>
+  <si>
+    <t>Test7</t>
+  </si>
+  <si>
+    <t>10698072</t>
+  </si>
+  <si>
+    <t>Uriah</t>
+  </si>
+  <si>
+    <t>Medhurst</t>
+  </si>
+  <si>
+    <t>Auto 66154525</t>
+  </si>
+  <si>
+    <t>Assistant Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test8</t>
+  </si>
+  <si>
+    <t>10698073</t>
+  </si>
+  <si>
+    <t>Abby</t>
+  </si>
+  <si>
+    <t>Becker</t>
+  </si>
+  <si>
+    <t>Auto 6021389</t>
+  </si>
+  <si>
+    <t>Department Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test9</t>
+  </si>
+  <si>
+    <t>10698074</t>
+  </si>
+  <si>
+    <t>Lindsey</t>
+  </si>
+  <si>
+    <t>Hagenes</t>
+  </si>
+  <si>
+    <t>Auto 51830818</t>
+  </si>
+  <si>
+    <t>In-Store P&amp;C Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test10</t>
+  </si>
+  <si>
+    <t>10698075</t>
+  </si>
+  <si>
+    <t>Emmalee</t>
+  </si>
+  <si>
+    <t>Kertzmann</t>
+  </si>
+  <si>
+    <t>In-Store P&amp;C Supervisor_NEW</t>
+  </si>
+  <si>
+    <t>250 Human Resources Retail</t>
+  </si>
+  <si>
+    <t>Supervizor</t>
+  </si>
+  <si>
+    <t>Test11</t>
+  </si>
+  <si>
+    <t>10698076</t>
+  </si>
+  <si>
+    <t>Ella</t>
+  </si>
+  <si>
+    <t>Jakubowski</t>
+  </si>
+  <si>
+    <t>Supervisor_NEW</t>
+  </si>
+  <si>
+    <t>253 Supervisors</t>
+  </si>
+  <si>
+    <t>Test12</t>
+  </si>
+  <si>
+    <t>10698078</t>
+  </si>
+  <si>
+    <t>Noelia</t>
+  </si>
+  <si>
+    <t>Cormier</t>
+  </si>
+  <si>
+    <t>Retail Assistant Cash Office_NEW</t>
+  </si>
+  <si>
+    <t>258 Cash Office</t>
+  </si>
+  <si>
+    <t>Test13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Jared Monahan' Employee:{10698079}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for getByLabel('Collective Agreement', { exact: true })[22m
+  [2m- waiting for locator('text=Onboarding Guide: Visual Merchandiser_NEW - Jared Monahan')[22m
 </t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>795 Store Management (Zogop Dogegy (10185858))</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Kelsie</t>
-  </si>
-  <si>
-    <t>Beatty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070-417-626 </t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Ljubljana</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@email.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>Auto 21947801</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>5 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
-  </si>
-  <si>
-    <t>Asistent v prodaji</t>
-  </si>
-  <si>
-    <t>IV.</t>
-  </si>
-  <si>
-    <t>Unique Master Citizen Number</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>01/01/2045</t>
-  </si>
-  <si>
-    <t>Slovenia Tax Number</t>
-  </si>
-  <si>
-    <t>01/01/2041</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Citizen (Slovenia)</t>
-  </si>
-  <si>
-    <t>TestBankOFSlovenia</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>SI56 2633 0001 2039 086</t>
-  </si>
-  <si>
-    <t>Grun Frun</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>SVN Monthly</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Gillian Bruen' Employee:{10697916}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//div[@data-automation-id=\'titleText\'][contains(./text(),\'Personal Information Change: Gillian Bruen\')]')[22m
-[2m  -   locator resolved to &lt;div class="css-t9tuu3" data-automation-id="titleText"&gt;Personal Information Change: Gillian Bruen (10697…&lt;/div&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" class="epf0sd81 css-1bc8v2p" data-…&gt;…&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>795 Recruitment (Zosig Depazi (10280602))</t>
-  </si>
-  <si>
-    <t>Gillian</t>
-  </si>
-  <si>
-    <t>Bruen</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Test3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Lester Ferry' Employee:{10697917}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"undefined"[39m
-Received: [31m"SVN Monthly"[39m</t>
-  </si>
-  <si>
-    <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
-  </si>
-  <si>
-    <t>Lester</t>
-  </si>
-  <si>
-    <t>Ferry</t>
-  </si>
-  <si>
-    <t>Fixed Term (Fixed Term)</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>3 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Test4</t>
-  </si>
-  <si>
-    <t>10697918</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Reagan</t>
-  </si>
-  <si>
-    <t>Hilpert</t>
-  </si>
-  <si>
-    <t>Auto 17527611</t>
-  </si>
-  <si>
-    <t>Team Manager - Retail_NEW</t>
-  </si>
-  <si>
-    <t>4 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>Test5</t>
-  </si>
-  <si>
-    <t>Jarrett</t>
-  </si>
-  <si>
-    <t>Blick</t>
-  </si>
-  <si>
-    <t>In-Store Visual Merchandising Assistant_NEW</t>
-  </si>
-  <si>
-    <t>256 Visual Merchandising</t>
-  </si>
-  <si>
-    <t>Test6</t>
-  </si>
-  <si>
-    <t>Maximo</t>
-  </si>
-  <si>
-    <t>Nienow</t>
-  </si>
-  <si>
-    <t>Auto 41216840</t>
-  </si>
-  <si>
-    <t>Strokovni sodelavec v kadrovski službi</t>
-  </si>
-  <si>
-    <t>V.</t>
-  </si>
-  <si>
-    <t>Test7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Berneice Krajcik' Employee:{10697880}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"undefined"[39m
-Received: [31m"Please select a Slovenia Pay Group"[39m</t>
-  </si>
-  <si>
-    <t>Berneice</t>
-  </si>
-  <si>
-    <t>Krajcik</t>
-  </si>
-  <si>
-    <t>Auto 14821156</t>
-  </si>
-  <si>
-    <t>Assistant Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Test8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Theresia Volkman' Employee:{10697886}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"undefined"[39m
-Received: [31m"Please select a Slovenia Pay Group"[39m</t>
-  </si>
-  <si>
-    <t>Theresia</t>
-  </si>
-  <si>
-    <t>Volkman</t>
-  </si>
-  <si>
-    <t>Auto 88685181</t>
-  </si>
-  <si>
-    <t>Department Manager_NEW</t>
-  </si>
-  <si>
-    <t>Test9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Muhammad Skiles' Employee:{10697887}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"undefined"[39m
-Received: [31m"SVN Monthly"[39m</t>
-  </si>
-  <si>
-    <t>Muhammad</t>
-  </si>
-  <si>
-    <t>Skiles</t>
-  </si>
-  <si>
-    <t>Auto 72343947</t>
-  </si>
-  <si>
-    <t>In-Store P&amp;C Manager_NEW</t>
-  </si>
-  <si>
-    <t>Test10</t>
-  </si>
-  <si>
-    <t>Pete</t>
-  </si>
-  <si>
-    <t>VonRueden</t>
-  </si>
-  <si>
-    <t>In-Store P&amp;C Supervisor_NEW</t>
-  </si>
-  <si>
-    <t>250 Human Resources Retail</t>
-  </si>
-  <si>
-    <t>Supervizor</t>
-  </si>
-  <si>
-    <t>Test11</t>
-  </si>
-  <si>
-    <t>Supervisor_NEW</t>
-  </si>
-  <si>
-    <t>253 Supervisors</t>
-  </si>
-  <si>
-    <t>Test12</t>
-  </si>
-  <si>
-    <t>Retail Assistant Cash Office_NEW</t>
-  </si>
-  <si>
-    <t>258 Cash Office</t>
-  </si>
-  <si>
-    <t>Test13</t>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>Monahan</t>
   </si>
   <si>
     <t>Visual Merchandiser_NEW</t>
@@ -956,16 +610,16 @@
     <t>Test14</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Branson Kirlin' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Declan West' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
   [2m- waiting for getByLabel('Work Shift')[22m
 </t>
   </si>
   <si>
-    <t>Branson</t>
-  </si>
-  <si>
-    <t>Kirlin</t>
+    <t>Declan</t>
+  </si>
+  <si>
+    <t>West</t>
   </si>
   <si>
     <t>Retail Assistant Stockroom_NEW</t>
@@ -977,14 +631,14 @@
     <t>Test15</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Keeley Welch' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.
-- Grade Profile is Missing     (Employee Compensation Event For Hire Employee)Alerts &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-18T05-49-41-141Z.png</t>
-  </si>
-  <si>
-    <t>Keeley</t>
-  </si>
-  <si>
-    <t>Welch</t>
+    <t>Test failed for 'Ola Franecki' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.
+- Grade Profile is Missing     (Employee Compensation Event For Hire Employee)Alerts &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-21T14-37-45-106Z.png</t>
+  </si>
+  <si>
+    <t>Ola</t>
+  </si>
+  <si>
+    <t>Franecki</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Supervisor_NEW</t>
@@ -996,58 +650,58 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1059,19 +713,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1083,7 +737,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1102,15 +756,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1121,14 +787,16 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1202,7 +870,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1223,7 +893,58 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1503,9 +1224,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BV16"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BV18"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" style="1" customWidth="1"/>
@@ -1555,7 +1276,7 @@
     <col min="47" max="47" width="22" style="1" customWidth="1"/>
     <col min="48" max="48" width="11.26953125" style="1" customWidth="1"/>
     <col min="49" max="49" width="36.26953125" style="1" customWidth="1"/>
-    <col min="50" max="50" width="20.08984375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="24" style="1" customWidth="1"/>
     <col min="51" max="51" width="13.90625" style="1" customWidth="1"/>
     <col min="52" max="52" width="17.6328125" style="2" customWidth="1"/>
     <col min="53" max="53" width="11.26953125" style="1" customWidth="1"/>
@@ -1582,7 +1303,7 @@
     <col min="74" max="74" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:74" s="3" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:74" s="3" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1806,7 +1527,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
@@ -1838,8 +1559,8 @@
         <v>79</v>
       </c>
       <c r="K2" s="17">
-        <f t="shared" ref="K2:K16" si="0">TODAY()-7</f>
-        <v>45727</v>
+        <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-7</f>
+        <v>45733</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>74</v>
@@ -1869,8 +1590,8 @@
         <v>79</v>
       </c>
       <c r="U2" s="22">
-        <f t="shared" ref="U2:U16" si="1">TODAY()-31</f>
-        <v>45703</v>
+        <f t="shared" ref="U2:U16" ca="1" si="1">TODAY()-31</f>
+        <v>45709</v>
       </c>
       <c r="V2" s="16" t="s">
         <v>84</v>
@@ -1915,20 +1636,20 @@
         <v>90</v>
       </c>
       <c r="AJ2" s="17">
-        <f t="shared" ref="AJ2:AL16" si="2">TODAY()-31</f>
-        <v>45703</v>
+        <f t="shared" ref="AJ2:AL16" ca="1" si="2">TODAY()-31</f>
+        <v>45709</v>
       </c>
       <c r="AK2" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL2" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM2" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM2" s="22" t="str">
         <f t="shared" ref="AM2:AM16" si="3">AF2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN2" s="16">
         <v>92</v>
@@ -1952,8 +1673,8 @@
         <v>90</v>
       </c>
       <c r="AU2" s="17">
-        <f t="shared" ref="AU2:AU16" si="4">TODAY()+7</f>
-        <v>45741</v>
+        <f t="shared" ref="AU2:AU16" ca="1" si="4">TODAY()+7</f>
+        <v>45747</v>
       </c>
       <c r="AV2" s="13" t="s">
         <v>74</v>
@@ -1962,7 +1683,8 @@
         <v>97</v>
       </c>
       <c r="AX2" s="30">
-        <v>2973000506964</v>
+        <f t="array" aca="1" ref="AX2:AX16" ca="1">_xlfn.RANDARRAY(15,1,1023456789000,9999999999999,TRUE)</f>
+        <v>5879589174643</v>
       </c>
       <c r="AY2" s="17" t="s">
         <v>98</v>
@@ -1977,7 +1699,8 @@
         <v>100</v>
       </c>
       <c r="BC2" s="31">
-        <v>93300889</v>
+        <f t="array" aca="1" ref="BC2:BC16" ca="1">_xlfn.RANDARRAY(15,1,12345678,99999999,TRUE)</f>
+        <v>90217606</v>
       </c>
       <c r="BD2" s="17" t="s">
         <v>98</v>
@@ -2019,7 +1742,8 @@
         <v>108</v>
       </c>
       <c r="BQ2" s="34">
-        <v>99730</v>
+        <f t="array" aca="1" ref="BQ2:BQ16" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
+        <v>24175</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -2031,14 +1755,14 @@
         <v>44562</v>
       </c>
       <c r="BU2" s="22">
-        <f t="shared" ref="BU2:BU16" si="5">TODAY()+365</f>
-        <v>46099</v>
+        <f t="shared" ref="BU2:BU16" ca="1" si="5">TODAY()+365</f>
+        <v>46105</v>
       </c>
       <c r="BV2" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -2070,8 +1794,8 @@
         <v>79</v>
       </c>
       <c r="K3" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>74</v>
@@ -2101,8 +1825,8 @@
         <v>79</v>
       </c>
       <c r="U3" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V3" s="16" t="s">
         <v>84</v>
@@ -2147,20 +1871,20 @@
         <v>90</v>
       </c>
       <c r="AJ3" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK3" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL3" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM3" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM3" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN3" s="16" t="s">
         <v>117</v>
@@ -2184,8 +1908,8 @@
         <v>90</v>
       </c>
       <c r="AU3" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV3" s="13" t="s">
         <v>74</v>
@@ -2194,7 +1918,8 @@
         <v>97</v>
       </c>
       <c r="AX3" s="30">
-        <v>2973000506965</v>
+        <f ca="1"/>
+        <v>9629308524529</v>
       </c>
       <c r="AY3" s="17" t="s">
         <v>98</v>
@@ -2209,7 +1934,8 @@
         <v>100</v>
       </c>
       <c r="BC3" s="31">
-        <v>93300890</v>
+        <f ca="1"/>
+        <v>32599431</v>
       </c>
       <c r="BD3" s="17" t="s">
         <v>98</v>
@@ -2251,7 +1977,8 @@
         <v>108</v>
       </c>
       <c r="BQ3" s="34">
-        <v>99731</v>
+        <f ca="1"/>
+        <v>30782</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -2263,14 +1990,14 @@
         <v>44562</v>
       </c>
       <c r="BU3" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV3" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -2302,8 +2029,8 @@
         <v>79</v>
       </c>
       <c r="K4" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>74</v>
@@ -2333,8 +2060,8 @@
         <v>79</v>
       </c>
       <c r="U4" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V4" s="16" t="s">
         <v>84</v>
@@ -2366,9 +2093,9 @@
       <c r="AE4" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="AF4" s="35">
-        <f>TODAY()+365</f>
-        <v>46099</v>
+      <c r="AF4" s="28">
+        <f ca="1">TODAY()+365</f>
+        <v>46105</v>
       </c>
       <c r="AG4" s="16" t="s">
         <v>92</v>
@@ -2380,20 +2107,20 @@
         <v>90</v>
       </c>
       <c r="AJ4" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK4" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL4" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AM4" s="22">
-        <f t="shared" si="3"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46105</v>
       </c>
       <c r="AN4" s="16" t="s">
         <v>117</v>
@@ -2417,8 +2144,8 @@
         <v>90</v>
       </c>
       <c r="AU4" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV4" s="13" t="s">
         <v>74</v>
@@ -2427,7 +2154,8 @@
         <v>97</v>
       </c>
       <c r="AX4" s="30">
-        <v>2973000506966</v>
+        <f ca="1"/>
+        <v>4535670695535</v>
       </c>
       <c r="AY4" s="17" t="s">
         <v>98</v>
@@ -2442,7 +2170,8 @@
         <v>100</v>
       </c>
       <c r="BC4" s="31">
-        <v>93300891</v>
+        <f ca="1"/>
+        <v>57464761</v>
       </c>
       <c r="BD4" s="17" t="s">
         <v>98</v>
@@ -2484,7 +2213,8 @@
         <v>108</v>
       </c>
       <c r="BQ4" s="34">
-        <v>99732</v>
+        <f ca="1"/>
+        <v>41501</v>
       </c>
       <c r="BR4" s="17">
         <v>44562</v>
@@ -2496,14 +2226,14 @@
         <v>44562</v>
       </c>
       <c r="BU4" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV4" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>128</v>
       </c>
@@ -2511,7 +2241,7 @@
         <v>129</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>73</v>
@@ -2520,10 +2250,10 @@
         <v>74</v>
       </c>
       <c r="F5" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>131</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>132</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>77</v>
@@ -2535,8 +2265,8 @@
         <v>79</v>
       </c>
       <c r="K5" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L5" s="13" t="s">
         <v>74</v>
@@ -2566,20 +2296,20 @@
         <v>79</v>
       </c>
       <c r="U5" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V5" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W5" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="X5" s="24" t="s">
         <v>124</v>
       </c>
       <c r="Y5" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z5" s="24" t="s">
         <v>125</v>
@@ -2597,11 +2327,11 @@
         <v>90</v>
       </c>
       <c r="AE5" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF5" s="35">
-        <f>TODAY()+365</f>
-        <v>46099</v>
+        <v>134</v>
+      </c>
+      <c r="AF5" s="28">
+        <f ca="1">TODAY()+365</f>
+        <v>46105</v>
       </c>
       <c r="AG5" s="16" t="s">
         <v>92</v>
@@ -2613,20 +2343,20 @@
         <v>90</v>
       </c>
       <c r="AJ5" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK5" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL5" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AM5" s="22">
-        <f t="shared" si="3"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46105</v>
       </c>
       <c r="AN5" s="16">
         <v>92</v>
@@ -2650,8 +2380,8 @@
         <v>90</v>
       </c>
       <c r="AU5" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV5" s="13" t="s">
         <v>74</v>
@@ -2660,7 +2390,8 @@
         <v>97</v>
       </c>
       <c r="AX5" s="30">
-        <v>2973000506967</v>
+        <f ca="1"/>
+        <v>6805196517561</v>
       </c>
       <c r="AY5" s="17" t="s">
         <v>98</v>
@@ -2675,7 +2406,8 @@
         <v>100</v>
       </c>
       <c r="BC5" s="31">
-        <v>93300892</v>
+        <f ca="1"/>
+        <v>70131589</v>
       </c>
       <c r="BD5" s="17" t="s">
         <v>98</v>
@@ -2717,7 +2449,8 @@
         <v>108</v>
       </c>
       <c r="BQ5" s="34">
-        <v>99733</v>
+        <f ca="1"/>
+        <v>57465</v>
       </c>
       <c r="BR5" s="17">
         <v>44562</v>
@@ -2729,18 +2462,23 @@
         <v>44562</v>
       </c>
       <c r="BU5" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV5" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D6" s="12" t="s">
         <v>121</v>
       </c>
@@ -2763,8 +2501,8 @@
         <v>79</v>
       </c>
       <c r="K6" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L6" s="13" t="s">
         <v>74</v>
@@ -2794,8 +2532,8 @@
         <v>79</v>
       </c>
       <c r="U6" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V6" s="16" t="s">
         <v>84</v>
@@ -2840,20 +2578,20 @@
         <v>90</v>
       </c>
       <c r="AJ6" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK6" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL6" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM6" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM6" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN6" s="16" t="s">
         <v>117</v>
@@ -2877,8 +2615,8 @@
         <v>90</v>
       </c>
       <c r="AU6" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV6" s="13" t="s">
         <v>74</v>
@@ -2887,7 +2625,8 @@
         <v>97</v>
       </c>
       <c r="AX6" s="30">
-        <v>2973000506968</v>
+        <f ca="1"/>
+        <v>3129804546869</v>
       </c>
       <c r="AY6" s="17" t="s">
         <v>98</v>
@@ -2902,7 +2641,8 @@
         <v>100</v>
       </c>
       <c r="BC6" s="31">
-        <v>93300893</v>
+        <f ca="1"/>
+        <v>85197506</v>
       </c>
       <c r="BD6" s="17" t="s">
         <v>98</v>
@@ -2944,7 +2684,8 @@
         <v>108</v>
       </c>
       <c r="BQ6" s="34">
-        <v>99734</v>
+        <f ca="1"/>
+        <v>34673</v>
       </c>
       <c r="BR6" s="17">
         <v>44562</v>
@@ -2956,18 +2697,23 @@
         <v>44562</v>
       </c>
       <c r="BU6" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV6" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="7" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="B7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D7" s="12" t="s">
         <v>73</v>
       </c>
@@ -2975,10 +2721,10 @@
         <v>74</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>77</v>
@@ -2990,8 +2736,8 @@
         <v>79</v>
       </c>
       <c r="K7" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>74</v>
@@ -3021,20 +2767,20 @@
         <v>79</v>
       </c>
       <c r="U7" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V7" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="X7" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y7" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z7" s="24" t="s">
         <v>88</v>
@@ -3067,20 +2813,20 @@
         <v>90</v>
       </c>
       <c r="AJ7" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK7" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL7" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM7" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM7" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN7" s="16">
         <v>92</v>
@@ -3092,10 +2838,10 @@
         <v>94</v>
       </c>
       <c r="AQ7" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AS7" s="13" t="s">
         <v>90</v>
@@ -3104,8 +2850,8 @@
         <v>90</v>
       </c>
       <c r="AU7" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV7" s="13" t="s">
         <v>74</v>
@@ -3114,7 +2860,8 @@
         <v>97</v>
       </c>
       <c r="AX7" s="30">
-        <v>2973000506969</v>
+        <f ca="1"/>
+        <v>3882424946312</v>
       </c>
       <c r="AY7" s="17" t="s">
         <v>98</v>
@@ -3129,7 +2876,8 @@
         <v>100</v>
       </c>
       <c r="BC7" s="31">
-        <v>93300894</v>
+        <f ca="1"/>
+        <v>89025441</v>
       </c>
       <c r="BD7" s="17" t="s">
         <v>98</v>
@@ -3171,7 +2919,8 @@
         <v>108</v>
       </c>
       <c r="BQ7" s="34">
-        <v>99735</v>
+        <f ca="1"/>
+        <v>15689</v>
       </c>
       <c r="BR7" s="17">
         <v>44562</v>
@@ -3183,484 +2932,490 @@
         <v>44562</v>
       </c>
       <c r="BU7" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV7" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="8" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
         <v>148</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>149</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8" s="14" t="s">
+      <c r="E8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="G8" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" s="18" t="s">
+      <c r="K8" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N8" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="40">
         <v>1542</v>
       </c>
-      <c r="Q8" s="16" t="s">
+      <c r="Q8" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="20" t="s">
+      <c r="R8" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="T8" s="16" t="s">
+      <c r="T8" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="U8" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
-      </c>
-      <c r="V8" s="16" t="s">
+      <c r="U8" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
+      </c>
+      <c r="V8" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="W8" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="X8" s="24" t="s">
+      <c r="W8" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="X8" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="Y8" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z8" s="24" t="s">
+      <c r="Y8" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z8" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="31">
         <v>795</v>
       </c>
-      <c r="AB8" s="25" t="s">
+      <c r="AB8" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="48">
         <v>40</v>
       </c>
-      <c r="AD8" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE8" s="19" t="s">
+      <c r="AD8" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE8" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="AF8" s="35">
-        <f>TODAY()+365</f>
-        <v>46099</v>
-      </c>
-      <c r="AG8" s="16" t="s">
+      <c r="AF8" s="50">
+        <f ca="1">TODAY()+365</f>
+        <v>46105</v>
+      </c>
+      <c r="AG8" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AH8" s="16" t="s">
+      <c r="AH8" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AI8" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ8" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+      <c r="AI8" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ8" s="41">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK8" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL8" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM8" s="22">
-        <f t="shared" si="3"/>
-        <v>46099</v>
-      </c>
-      <c r="AN8" s="16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM8" s="46">
+        <f t="shared" ca="1" si="3"/>
+        <v>46105</v>
+      </c>
+      <c r="AN8" s="40">
         <v>92</v>
       </c>
-      <c r="AO8" s="24">
+      <c r="AO8" s="47">
         <v>251</v>
       </c>
-      <c r="AP8" s="24" t="s">
+      <c r="AP8" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="AQ8" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="AR8" s="19" t="s">
+      <c r="AQ8" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="AS8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU8" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
-      </c>
-      <c r="AV8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW8" s="29" t="s">
+      <c r="AR8" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS8" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT8" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU8" s="41">
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
+      </c>
+      <c r="AV8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW8" s="51" t="s">
         <v>97</v>
       </c>
       <c r="AX8" s="30">
-        <v>2973000506970</v>
-      </c>
-      <c r="AY8" s="17" t="s">
+        <f ca="1"/>
+        <v>9824543293334</v>
+      </c>
+      <c r="AY8" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AZ8" s="17" t="s">
+      <c r="AZ8" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="BA8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB8" s="29" t="s">
+      <c r="BA8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB8" s="51" t="s">
         <v>100</v>
       </c>
       <c r="BC8" s="31">
-        <v>93300895</v>
-      </c>
-      <c r="BD8" s="17" t="s">
+        <f ca="1"/>
+        <v>18676007</v>
+      </c>
+      <c r="BD8" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BE8" s="17" t="s">
+      <c r="BE8" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="BF8" s="19" t="s">
+      <c r="BF8" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BG8" s="17" t="s">
+      <c r="BG8" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BH8" s="13" t="s">
+      <c r="BH8" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="BI8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ8" s="13" t="s">
+      <c r="BI8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ8" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BK8" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL8" s="13" t="s">
+      <c r="BK8" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL8" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BM8" s="33" t="s">
+      <c r="BM8" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="BN8" s="13" t="s">
+      <c r="BN8" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="BO8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP8" s="13" t="s">
+      <c r="BO8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP8" s="34" t="s">
         <v>108</v>
       </c>
       <c r="BQ8" s="34">
-        <v>99736</v>
-      </c>
-      <c r="BR8" s="17">
+        <f ca="1"/>
+        <v>75678</v>
+      </c>
+      <c r="BR8" s="41">
         <v>44562</v>
       </c>
-      <c r="BS8" s="17">
+      <c r="BS8" s="41">
         <v>47119</v>
       </c>
-      <c r="BT8" s="22">
+      <c r="BT8" s="46">
         <v>44562</v>
       </c>
-      <c r="BU8" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
-      </c>
-      <c r="BV8" s="16" t="s">
+      <c r="BU8" s="46">
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
+      </c>
+      <c r="BV8" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
         <v>154</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="E9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="G9" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M9" s="18" t="s">
+      <c r="K9" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N9" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="40">
         <v>1542</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="R9" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="S9" s="21" t="s">
+      <c r="S9" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="T9" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="U9" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
-      </c>
-      <c r="V9" s="16" t="s">
+      <c r="U9" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
+      </c>
+      <c r="V9" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="W9" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="X9" s="24" t="s">
+      <c r="W9" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="X9" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="Y9" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z9" s="24" t="s">
+      <c r="Y9" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z9" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="AA9" s="25">
+      <c r="AA9" s="31">
         <v>795</v>
       </c>
-      <c r="AB9" s="25" t="s">
+      <c r="AB9" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="AC9" s="26">
+      <c r="AC9" s="48">
         <v>20</v>
       </c>
-      <c r="AD9" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE9" s="19" t="s">
+      <c r="AD9" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE9" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="AF9" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG9" s="16" t="s">
+      <c r="AF9" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG9" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AH9" s="16" t="s">
+      <c r="AH9" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AI9" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ9" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+      <c r="AI9" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ9" s="41">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK9" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL9" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM9" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM9" s="46" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
-      </c>
-      <c r="AN9" s="16">
+        <v>N/A</v>
+      </c>
+      <c r="AN9" s="40">
         <v>92</v>
       </c>
-      <c r="AO9" s="24">
+      <c r="AO9" s="47">
         <v>251</v>
       </c>
-      <c r="AP9" s="24" t="s">
+      <c r="AP9" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="AQ9" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="AR9" s="19" t="s">
+      <c r="AQ9" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="AS9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU9" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
-      </c>
-      <c r="AV9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW9" s="29" t="s">
+      <c r="AR9" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS9" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT9" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU9" s="41">
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
+      </c>
+      <c r="AV9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW9" s="51" t="s">
         <v>97</v>
       </c>
       <c r="AX9" s="30">
-        <v>2973000506971</v>
-      </c>
-      <c r="AY9" s="17" t="s">
+        <f ca="1"/>
+        <v>6574353571659</v>
+      </c>
+      <c r="AY9" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AZ9" s="17" t="s">
+      <c r="AZ9" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="BA9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB9" s="29" t="s">
+      <c r="BA9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB9" s="51" t="s">
         <v>100</v>
       </c>
       <c r="BC9" s="31">
-        <v>93300896</v>
-      </c>
-      <c r="BD9" s="17" t="s">
+        <f ca="1"/>
+        <v>78589868</v>
+      </c>
+      <c r="BD9" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BE9" s="17" t="s">
+      <c r="BE9" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="BF9" s="19" t="s">
+      <c r="BF9" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BG9" s="17" t="s">
+      <c r="BG9" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BH9" s="13" t="s">
+      <c r="BH9" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="BI9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ9" s="13" t="s">
+      <c r="BI9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ9" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BK9" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL9" s="13" t="s">
+      <c r="BK9" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL9" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BM9" s="33" t="s">
+      <c r="BM9" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="BN9" s="13" t="s">
+      <c r="BN9" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="BO9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP9" s="13" t="s">
+      <c r="BO9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP9" s="34" t="s">
         <v>108</v>
       </c>
       <c r="BQ9" s="34">
-        <v>99737</v>
-      </c>
-      <c r="BR9" s="17">
+        <f ca="1"/>
+        <v>51690</v>
+      </c>
+      <c r="BR9" s="41">
         <v>44562</v>
       </c>
-      <c r="BS9" s="17">
+      <c r="BS9" s="41">
         <v>47119</v>
       </c>
-      <c r="BT9" s="22">
+      <c r="BT9" s="46">
         <v>44562</v>
       </c>
-      <c r="BU9" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
-      </c>
-      <c r="BV9" s="16" t="s">
+      <c r="BU9" s="46">
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
+      </c>
+      <c r="BV9" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>72</v>
@@ -3672,10 +3427,10 @@
         <v>74</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>77</v>
@@ -3687,8 +3442,8 @@
         <v>79</v>
       </c>
       <c r="K10" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>74</v>
@@ -3718,20 +3473,20 @@
         <v>79</v>
       </c>
       <c r="U10" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V10" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X10" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y10" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z10" s="24" t="s">
         <v>88</v>
@@ -3764,20 +3519,20 @@
         <v>90</v>
       </c>
       <c r="AJ10" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK10" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL10" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM10" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM10" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN10" s="16">
         <v>92</v>
@@ -3789,10 +3544,10 @@
         <v>94</v>
       </c>
       <c r="AQ10" s="24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AR10" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AS10" s="13" t="s">
         <v>90</v>
@@ -3801,8 +3556,8 @@
         <v>90</v>
       </c>
       <c r="AU10" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV10" s="13" t="s">
         <v>74</v>
@@ -3811,7 +3566,8 @@
         <v>97</v>
       </c>
       <c r="AX10" s="30">
-        <v>2973000506972</v>
+        <f ca="1"/>
+        <v>3850767557935</v>
       </c>
       <c r="AY10" s="17" t="s">
         <v>98</v>
@@ -3826,7 +3582,8 @@
         <v>100</v>
       </c>
       <c r="BC10" s="31">
-        <v>93300897</v>
+        <f ca="1"/>
+        <v>74805827</v>
       </c>
       <c r="BD10" s="17" t="s">
         <v>98</v>
@@ -3868,7 +3625,8 @@
         <v>108</v>
       </c>
       <c r="BQ10" s="34">
-        <v>99738</v>
+        <f ca="1"/>
+        <v>84181</v>
       </c>
       <c r="BR10" s="17">
         <v>44562</v>
@@ -3880,253 +3638,270 @@
         <v>44562</v>
       </c>
       <c r="BU10" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV10" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12" t="s">
+    <row r="11" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" s="15" t="s">
+      <c r="E11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="K11" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M11" s="18" t="s">
+      <c r="K11" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M11" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O11" s="19" t="s">
+      <c r="O11" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="40">
         <v>1542</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="R11" s="20" t="s">
+      <c r="R11" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="S11" s="21" t="s">
+      <c r="S11" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="T11" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="U11" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
-      </c>
-      <c r="V11" s="16" t="s">
+      <c r="U11" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
+      </c>
+      <c r="V11" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="W11" s="23" t="s">
+      <c r="W11" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="X11" s="24" t="s">
+      <c r="X11" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="Y11" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z11" s="24" t="s">
+      <c r="Y11" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z11" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="25">
+      <c r="AA11" s="31">
         <v>795</v>
       </c>
-      <c r="AB11" s="25" t="s">
+      <c r="AB11" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="AC11" s="26">
+      <c r="AC11" s="48">
         <v>40</v>
       </c>
-      <c r="AD11" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE11" s="19" t="s">
+      <c r="AD11" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE11" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="AF11" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="AG11" s="16" t="s">
+      <c r="AF11" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG11" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AH11" s="16" t="s">
+      <c r="AH11" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AI11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ11" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+      <c r="AI11" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ11" s="41">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK11" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL11" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM11" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM11" s="46" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
-      </c>
-      <c r="AN11" s="16" t="s">
+        <v>N/A</v>
+      </c>
+      <c r="AN11" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="AO11" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="AP11" s="24" t="s">
+      <c r="AO11" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="AP11" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="AQ11" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="AR11" s="19" t="s">
+      <c r="AQ11" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="AR11" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="AS11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU11" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
-      </c>
-      <c r="AV11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW11" s="29" t="s">
+      <c r="AS11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU11" s="41">
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
+      </c>
+      <c r="AV11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW11" s="51" t="s">
         <v>97</v>
       </c>
       <c r="AX11" s="30">
-        <v>2973000506973</v>
-      </c>
-      <c r="AY11" s="17" t="s">
+        <f ca="1"/>
+        <v>8820339871414</v>
+      </c>
+      <c r="AY11" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AZ11" s="17" t="s">
+      <c r="AZ11" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="BA11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB11" s="29" t="s">
+      <c r="BA11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB11" s="51" t="s">
         <v>100</v>
       </c>
       <c r="BC11" s="31">
-        <v>93300898</v>
-      </c>
-      <c r="BD11" s="17" t="s">
+        <f ca="1"/>
+        <v>14120630</v>
+      </c>
+      <c r="BD11" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BE11" s="17" t="s">
+      <c r="BE11" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="BF11" s="19" t="s">
+      <c r="BF11" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BG11" s="17" t="s">
+      <c r="BG11" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BH11" s="13" t="s">
+      <c r="BH11" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="BI11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ11" s="13" t="s">
+      <c r="BI11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ11" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BK11" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL11" s="13" t="s">
+      <c r="BK11" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL11" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BM11" s="33" t="s">
+      <c r="BM11" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="BN11" s="13" t="s">
+      <c r="BN11" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="BO11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP11" s="13" t="s">
+      <c r="BO11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP11" s="34" t="s">
         <v>108</v>
       </c>
       <c r="BQ11" s="34">
-        <v>99739</v>
-      </c>
-      <c r="BR11" s="17">
+        <f ca="1"/>
+        <v>56854</v>
+      </c>
+      <c r="BR11" s="41">
         <v>44562</v>
       </c>
-      <c r="BS11" s="17">
+      <c r="BS11" s="41">
         <v>47119</v>
       </c>
-      <c r="BT11" s="22">
+      <c r="BT11" s="46">
         <v>44562</v>
       </c>
-      <c r="BU11" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
-      </c>
-      <c r="BV11" s="16" t="s">
+      <c r="BU11" s="46">
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
+      </c>
+      <c r="BV11" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="12" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="11"/>
+        <v>173</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>72</v>
+      </c>
       <c r="D12" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="F12" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="H12" s="15" t="s">
         <v>77</v>
       </c>
@@ -4137,8 +3912,8 @@
         <v>79</v>
       </c>
       <c r="K12" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>74</v>
@@ -4168,8 +3943,8 @@
         <v>79</v>
       </c>
       <c r="U12" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V12" s="16" t="s">
         <v>84</v>
@@ -4181,7 +3956,7 @@
         <v>86</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Z12" s="24" t="s">
         <v>125</v>
@@ -4214,32 +3989,32 @@
         <v>90</v>
       </c>
       <c r="AJ12" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK12" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL12" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM12" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM12" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN12" s="16" t="s">
         <v>117</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AP12" s="24" t="s">
         <v>94</v>
       </c>
       <c r="AQ12" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AR12" s="19" t="s">
         <v>96</v>
@@ -4251,8 +4026,8 @@
         <v>90</v>
       </c>
       <c r="AU12" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV12" s="13" t="s">
         <v>74</v>
@@ -4261,7 +4036,8 @@
         <v>97</v>
       </c>
       <c r="AX12" s="30">
-        <v>2973000506974</v>
+        <f ca="1"/>
+        <v>6329089829318</v>
       </c>
       <c r="AY12" s="17" t="s">
         <v>98</v>
@@ -4276,7 +4052,8 @@
         <v>100</v>
       </c>
       <c r="BC12" s="31">
-        <v>93300899</v>
+        <f ca="1"/>
+        <v>44951213</v>
       </c>
       <c r="BD12" s="17" t="s">
         <v>98</v>
@@ -4318,7 +4095,8 @@
         <v>108</v>
       </c>
       <c r="BQ12" s="34">
-        <v>99740</v>
+        <f ca="1"/>
+        <v>35567</v>
       </c>
       <c r="BR12" s="17">
         <v>44562</v>
@@ -4330,250 +4108,271 @@
         <v>44562</v>
       </c>
       <c r="BU12" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV12" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="s">
+    <row r="13" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15" t="s">
+      <c r="E13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="K13" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M13" s="18" t="s">
+      <c r="K13" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="40">
         <v>1542</v>
       </c>
-      <c r="Q13" s="16" t="s">
+      <c r="Q13" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="R13" s="20" t="s">
+      <c r="R13" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="S13" s="21" t="s">
+      <c r="S13" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="16" t="s">
+      <c r="T13" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="U13" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
-      </c>
-      <c r="V13" s="16" t="s">
+      <c r="U13" s="46">
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
+      </c>
+      <c r="V13" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="W13" s="23" t="s">
+      <c r="W13" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="X13" s="24" t="s">
+      <c r="X13" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="Y13" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z13" s="24" t="s">
+      <c r="Y13" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z13" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="31">
         <v>795</v>
       </c>
-      <c r="AB13" s="25" t="s">
+      <c r="AB13" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="AC13" s="26">
+      <c r="AC13" s="48">
         <v>25</v>
       </c>
-      <c r="AD13" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE13" s="19" t="s">
+      <c r="AD13" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE13" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="AF13" s="35">
-        <f>TODAY()+365</f>
-        <v>46099</v>
-      </c>
-      <c r="AG13" s="16" t="s">
+      <c r="AF13" s="50">
+        <f ca="1">TODAY()+365</f>
+        <v>46105</v>
+      </c>
+      <c r="AG13" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="AH13" s="16" t="s">
+      <c r="AH13" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="AI13" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ13" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+      <c r="AI13" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ13" s="41">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK13" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL13" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM13" s="22">
-        <f t="shared" si="3"/>
-        <v>46099</v>
-      </c>
-      <c r="AN13" s="16" t="s">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM13" s="46">
+        <f t="shared" ca="1" si="3"/>
+        <v>46105</v>
+      </c>
+      <c r="AN13" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="AO13" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="AP13" s="24" t="s">
+      <c r="AO13" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="AP13" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="AQ13" s="24" t="s">
+      <c r="AQ13" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="AR13" s="19" t="s">
+      <c r="AR13" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="AS13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU13" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
-      </c>
-      <c r="AV13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW13" s="29" t="s">
+      <c r="AS13" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT13" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU13" s="41">
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
+      </c>
+      <c r="AV13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW13" s="51" t="s">
         <v>97</v>
       </c>
       <c r="AX13" s="30">
-        <v>2973000506975</v>
-      </c>
-      <c r="AY13" s="17" t="s">
+        <f ca="1"/>
+        <v>3437783974897</v>
+      </c>
+      <c r="AY13" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="AZ13" s="17" t="s">
+      <c r="AZ13" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="BA13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BB13" s="29" t="s">
+      <c r="BA13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB13" s="51" t="s">
         <v>100</v>
       </c>
       <c r="BC13" s="31">
-        <v>93300900</v>
-      </c>
-      <c r="BD13" s="17" t="s">
+        <f ca="1"/>
+        <v>64831588</v>
+      </c>
+      <c r="BD13" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BE13" s="17" t="s">
+      <c r="BE13" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="BF13" s="19" t="s">
+      <c r="BF13" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="BG13" s="17" t="s">
+      <c r="BG13" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="BH13" s="13" t="s">
+      <c r="BH13" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="BI13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BJ13" s="13" t="s">
+      <c r="BI13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BJ13" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="BK13" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="BL13" s="13" t="s">
+      <c r="BK13" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL13" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="BM13" s="33" t="s">
+      <c r="BM13" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="BN13" s="13" t="s">
+      <c r="BN13" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="BO13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP13" s="13" t="s">
+      <c r="BO13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP13" s="34" t="s">
         <v>108</v>
       </c>
       <c r="BQ13" s="34">
-        <v>99741</v>
-      </c>
-      <c r="BR13" s="17">
+        <f ca="1"/>
+        <v>18196</v>
+      </c>
+      <c r="BR13" s="41">
         <v>44562</v>
       </c>
-      <c r="BS13" s="17">
+      <c r="BS13" s="41">
         <v>47119</v>
       </c>
-      <c r="BT13" s="22">
+      <c r="BT13" s="46">
         <v>44562</v>
       </c>
-      <c r="BU13" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
-      </c>
-      <c r="BV13" s="16" t="s">
+      <c r="BU13" s="46">
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
+      </c>
+      <c r="BV13" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="D14" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="F14" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>189</v>
+      </c>
       <c r="H14" s="15" t="s">
         <v>77</v>
       </c>
@@ -4584,8 +4383,8 @@
         <v>79</v>
       </c>
       <c r="K14" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>74</v>
@@ -4615,8 +4414,8 @@
         <v>79</v>
       </c>
       <c r="U14" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V14" s="16" t="s">
         <v>84</v>
@@ -4628,7 +4427,7 @@
         <v>124</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Z14" s="24" t="s">
         <v>88</v>
@@ -4648,9 +4447,9 @@
       <c r="AE14" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="AF14" s="35">
-        <f>TODAY()+365</f>
-        <v>46099</v>
+      <c r="AF14" s="28">
+        <f ca="1">TODAY()+365</f>
+        <v>46105</v>
       </c>
       <c r="AG14" s="16" t="s">
         <v>92</v>
@@ -4662,20 +4461,20 @@
         <v>90</v>
       </c>
       <c r="AJ14" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK14" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL14" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AM14" s="22">
-        <f t="shared" si="3"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>46105</v>
       </c>
       <c r="AN14" s="16" t="s">
         <v>117</v>
@@ -4699,8 +4498,8 @@
         <v>90</v>
       </c>
       <c r="AU14" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV14" s="13" t="s">
         <v>74</v>
@@ -4709,7 +4508,8 @@
         <v>97</v>
       </c>
       <c r="AX14" s="30">
-        <v>2973000506976</v>
+        <f ca="1"/>
+        <v>3941794048959</v>
       </c>
       <c r="AY14" s="17" t="s">
         <v>98</v>
@@ -4724,7 +4524,8 @@
         <v>100</v>
       </c>
       <c r="BC14" s="31">
-        <v>93300901</v>
+        <f ca="1"/>
+        <v>82567804</v>
       </c>
       <c r="BD14" s="17" t="s">
         <v>98</v>
@@ -4766,7 +4567,8 @@
         <v>108</v>
       </c>
       <c r="BQ14" s="34">
-        <v>99742</v>
+        <f ca="1"/>
+        <v>35646</v>
       </c>
       <c r="BR14" s="17">
         <v>44562</v>
@@ -4778,22 +4580,22 @@
         <v>44562</v>
       </c>
       <c r="BU14" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV14" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>121</v>
@@ -4802,10 +4604,10 @@
         <v>74</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>77</v>
@@ -4817,8 +4619,8 @@
         <v>79</v>
       </c>
       <c r="K15" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>74</v>
@@ -4848,8 +4650,8 @@
         <v>79</v>
       </c>
       <c r="U15" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V15" s="16" t="s">
         <v>84</v>
@@ -4861,7 +4663,7 @@
         <v>86</v>
       </c>
       <c r="Y15" s="24" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="Z15" s="24" t="s">
         <v>125</v>
@@ -4894,26 +4696,26 @@
         <v>90</v>
       </c>
       <c r="AJ15" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK15" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL15" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM15" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM15" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN15" s="16" t="s">
         <v>117</v>
       </c>
       <c r="AO15" s="24" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AP15" s="24" t="s">
         <v>94</v>
@@ -4931,8 +4733,8 @@
         <v>90</v>
       </c>
       <c r="AU15" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV15" s="13" t="s">
         <v>74</v>
@@ -4941,7 +4743,8 @@
         <v>97</v>
       </c>
       <c r="AX15" s="30">
-        <v>2973000506977</v>
+        <f ca="1"/>
+        <v>6519217663694</v>
       </c>
       <c r="AY15" s="17" t="s">
         <v>98</v>
@@ -4956,7 +4759,8 @@
         <v>100</v>
       </c>
       <c r="BC15" s="31">
-        <v>93300902</v>
+        <f ca="1"/>
+        <v>61320857</v>
       </c>
       <c r="BD15" s="17" t="s">
         <v>98</v>
@@ -4998,7 +4802,8 @@
         <v>108</v>
       </c>
       <c r="BQ15" s="34">
-        <v>99743</v>
+        <f ca="1"/>
+        <v>75176</v>
       </c>
       <c r="BR15" s="17">
         <v>44562</v>
@@ -5010,22 +4815,22 @@
         <v>44562</v>
       </c>
       <c r="BU15" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV15" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" ht="15.65" customHeight="1" spans="1:74" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>121</v>
@@ -5034,10 +4839,10 @@
         <v>74</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>77</v>
@@ -5049,8 +4854,8 @@
         <v>79</v>
       </c>
       <c r="K16" s="17">
-        <f t="shared" si="0"/>
-        <v>45727</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45733</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>74</v>
@@ -5080,8 +4885,8 @@
         <v>79</v>
       </c>
       <c r="U16" s="22">
-        <f t="shared" si="1"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45709</v>
       </c>
       <c r="V16" s="16" t="s">
         <v>84</v>
@@ -5093,7 +4898,7 @@
         <v>86</v>
       </c>
       <c r="Y16" s="24" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Z16" s="24" t="s">
         <v>88</v>
@@ -5126,20 +4931,20 @@
         <v>90</v>
       </c>
       <c r="AJ16" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AK16" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
       </c>
       <c r="AL16" s="17">
-        <f t="shared" si="2"/>
-        <v>45703</v>
-      </c>
-      <c r="AM16" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>45709</v>
+      </c>
+      <c r="AM16" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AN16" s="16" t="s">
         <v>117</v>
@@ -5151,7 +4956,7 @@
         <v>94</v>
       </c>
       <c r="AQ16" s="24" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="AR16" s="19" t="s">
         <v>96</v>
@@ -5163,8 +4968,8 @@
         <v>90</v>
       </c>
       <c r="AU16" s="17">
-        <f t="shared" si="4"/>
-        <v>45741</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>45747</v>
       </c>
       <c r="AV16" s="13" t="s">
         <v>74</v>
@@ -5173,7 +4978,8 @@
         <v>97</v>
       </c>
       <c r="AX16" s="30">
-        <v>2973000506978</v>
+        <f ca="1"/>
+        <v>5300785576112</v>
       </c>
       <c r="AY16" s="17" t="s">
         <v>98</v>
@@ -5188,7 +4994,8 @@
         <v>100</v>
       </c>
       <c r="BC16" s="31">
-        <v>93300903</v>
+        <f ca="1"/>
+        <v>85925571</v>
       </c>
       <c r="BD16" s="17" t="s">
         <v>98</v>
@@ -5230,7 +5037,8 @@
         <v>108</v>
       </c>
       <c r="BQ16" s="34">
-        <v>99744</v>
+        <f ca="1"/>
+        <v>46500</v>
       </c>
       <c r="BR16" s="17">
         <v>44562</v>
@@ -5242,82 +5050,59 @@
         <v>44562</v>
       </c>
       <c r="BU16" s="22">
-        <f t="shared" si="5"/>
-        <v>46099</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>46105</v>
       </c>
       <c r="BV16" s="16" t="s">
         <v>109</v>
       </c>
     </row>
+    <row r="17" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF17" s="54"/>
+      <c r="AL17" s="17"/>
+    </row>
+    <row r="18" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AL18" s="17"/>
+    </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH10:AH16">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH10:AH16 V10:V16 T10:T16 Q10:Q16 J10:J16 BL10:BL16" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL10:BL16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q10:Q16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH16 V2:V16 T2:T16 Q2:Q16 J2:J16 BL2:BL16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
-    <hyperlink ref="S4" r:id="rId3"/>
-    <hyperlink ref="S5" r:id="rId4"/>
-    <hyperlink ref="S6" r:id="rId5"/>
-    <hyperlink ref="AD6" r:id="rId6"/>
-    <hyperlink ref="S7" r:id="rId7"/>
-    <hyperlink ref="AD7" r:id="rId8"/>
-    <hyperlink ref="S8" r:id="rId9"/>
-    <hyperlink ref="AD8" r:id="rId10"/>
-    <hyperlink ref="S9" r:id="rId11"/>
-    <hyperlink ref="AD9" r:id="rId12"/>
-    <hyperlink ref="S10" r:id="rId13"/>
-    <hyperlink ref="AD10" r:id="rId14"/>
-    <hyperlink ref="S11" r:id="rId15"/>
-    <hyperlink ref="AD11" r:id="rId16"/>
-    <hyperlink ref="S12" r:id="rId17"/>
-    <hyperlink ref="AD12" r:id="rId18"/>
-    <hyperlink ref="S13" r:id="rId19"/>
-    <hyperlink ref="AD13" r:id="rId20"/>
-    <hyperlink ref="S14" r:id="rId21"/>
-    <hyperlink ref="AD14" r:id="rId22"/>
-    <hyperlink ref="S15" r:id="rId23"/>
-    <hyperlink ref="AD15" r:id="rId24"/>
-    <hyperlink ref="S16" r:id="rId25"/>
-    <hyperlink ref="AD16" r:id="rId26"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="S5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="S6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="AD6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="S7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="AD7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="S8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="AD8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="S9" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="AD9" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="S10" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="AD10" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="S11" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="AD11" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="S12" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="AD12" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="S13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="AD13" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="S14" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="AD14" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="S15" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="AD15" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="S16" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="AD16" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Hires/TestDataSloveniaMKv1.xlsx
+++ b/Data/Hires/TestDataSloveniaMKv1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{3BDC4FFC-8847-4F75-A8A0-26E78603E1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{010A94B2-E573-40BF-B6FF-36154ED89136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="191">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -244,190 +244,190 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698062</t>
+    <t>Test failed for 'Eden Rogahn' Employee: Errors and AlertsErrorsPage ErrorSorry, the data you requested could not be found. Please refresh your page.ErrorAllowance Amount is required.ErrorAllowance Amount is required.Alerts &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_MK/WorkdayFailedScreenshot/2025-03-25T10-19-24-088Z.png</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>795 Store Management (Zogop Dogegy (On Leave) (10185858))</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Eden</t>
+  </si>
+  <si>
+    <t>Rogahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">070-417-626 </t>
+  </si>
+  <si>
+    <t>Landline</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Automation Street Name</t>
+  </si>
+  <si>
+    <t>Ljubljana</t>
+  </si>
+  <si>
+    <t>Street Address</t>
+  </si>
+  <si>
+    <t>Test@email.com</t>
+  </si>
+  <si>
+    <t>New Hire</t>
+  </si>
+  <si>
+    <t>Auto 9148281</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>5 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
+  </si>
+  <si>
+    <t>Asistent v prodaji</t>
+  </si>
+  <si>
+    <t>IV.</t>
+  </si>
+  <si>
+    <t>Unique Master Citizen Number</t>
+  </si>
+  <si>
+    <t>01/01/1999</t>
+  </si>
+  <si>
+    <t>01/01/2045</t>
+  </si>
+  <si>
+    <t>Slovenia Tax Number</t>
+  </si>
+  <si>
+    <t>01/01/2041</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Citizen (Slovenia)</t>
+  </si>
+  <si>
+    <t>TestBankOFSlovenia</t>
+  </si>
+  <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>SI56 2633 0001 2039 086</t>
+  </si>
+  <si>
+    <t>Grun Frun</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>SVN Monthly</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>10698135</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
+    <t>795 Recruitment (Zosig Depazi (10280602))</t>
+  </si>
+  <si>
+    <t>Carmel</t>
+  </si>
+  <si>
+    <t>Hane</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>94 Retail Operatives</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
+  </si>
+  <si>
+    <t>Jensen</t>
+  </si>
+  <si>
+    <t>O'Connell</t>
+  </si>
+  <si>
+    <t>Fixed Term (Fixed Term)</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>3 Days (Slovenia)</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
     <t>795 Store Management (Zogop Dogegy (10185858))</t>
   </si>
   <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Parker</t>
-  </si>
-  <si>
-    <t>Halvorson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">070-417-626 </t>
-  </si>
-  <si>
-    <t>Landline</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>Automation Street Name</t>
-  </si>
-  <si>
-    <t>Ljubljana</t>
-  </si>
-  <si>
-    <t>Street Address</t>
-  </si>
-  <si>
-    <t>Test@email.com</t>
-  </si>
-  <si>
-    <t>New Hire</t>
-  </si>
-  <si>
-    <t>Auto 95021107</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>Store Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>5 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>0- Ne gre za zaposlitev po ZUTD-A ali ZIUPTDSV</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
-  </si>
-  <si>
-    <t>Asistent v prodaji</t>
-  </si>
-  <si>
-    <t>IV.</t>
-  </si>
-  <si>
-    <t>Unique Master Citizen Number</t>
-  </si>
-  <si>
-    <t>01/01/1999</t>
-  </si>
-  <si>
-    <t>01/01/2045</t>
-  </si>
-  <si>
-    <t>Slovenia Tax Number</t>
-  </si>
-  <si>
-    <t>01/01/2041</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Citizen (Slovenia)</t>
-  </si>
-  <si>
-    <t>TestBankOFSlovenia</t>
-  </si>
-  <si>
-    <t>Checking</t>
-  </si>
-  <si>
-    <t>SI56 2633 0001 2039 086</t>
-  </si>
-  <si>
-    <t>Grun Frun</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>SVN Monthly</t>
-  </si>
-  <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>10698063</t>
-  </si>
-  <si>
-    <t>795 Recruitment (Zosig Depazi (10280602))</t>
-  </si>
-  <si>
-    <t>Mittie</t>
-  </si>
-  <si>
-    <t>Tillman</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>94 Retail Operatives</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>Test3</t>
-  </si>
-  <si>
-    <t>10698065</t>
-  </si>
-  <si>
-    <t>795 Retail Team 1 (Zogop Dogegy (10185858) (Inherited))</t>
-  </si>
-  <si>
-    <t>Aurore</t>
-  </si>
-  <si>
-    <t>Kreiger</t>
-  </si>
-  <si>
-    <t>Fixed Term (Fixed Term)</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>3 Days (Slovenia)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Test4</t>
-  </si>
-  <si>
-    <t>10698066</t>
-  </si>
-  <si>
-    <t>Antwon</t>
-  </si>
-  <si>
-    <t>Johns</t>
-  </si>
-  <si>
-    <t>Auto 5780199</t>
+    <t>Jairo</t>
+  </si>
+  <si>
+    <t>Gerhold</t>
+  </si>
+  <si>
+    <t>Auto 13582723</t>
   </si>
   <si>
     <t>Team Manager - Retail_NEW</t>
@@ -439,13 +439,10 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>10698068</t>
-  </si>
-  <si>
-    <t>Rebeka</t>
-  </si>
-  <si>
-    <t>Watsica</t>
+    <t>Fritz</t>
+  </si>
+  <si>
+    <t>Bayer</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Assistant_NEW</t>
@@ -457,16 +454,13 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10698070</t>
-  </si>
-  <si>
-    <t>Aron</t>
-  </si>
-  <si>
-    <t>Armstrong-McKenzie</t>
-  </si>
-  <si>
-    <t>Auto 7225502</t>
+    <t>Christopher</t>
+  </si>
+  <si>
+    <t>Schuppe</t>
+  </si>
+  <si>
+    <t>Auto 56790541</t>
   </si>
   <si>
     <t>Strokovni sodelavec v kadrovski službi</t>
@@ -478,16 +472,13 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10698072</t>
-  </si>
-  <si>
-    <t>Uriah</t>
-  </si>
-  <si>
-    <t>Medhurst</t>
-  </si>
-  <si>
-    <t>Auto 66154525</t>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t>Moen</t>
+  </si>
+  <si>
+    <t>Auto 67393007</t>
   </si>
   <si>
     <t>Assistant Store Manager_NEW</t>
@@ -496,16 +487,13 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10698073</t>
-  </si>
-  <si>
-    <t>Abby</t>
-  </si>
-  <si>
-    <t>Becker</t>
-  </si>
-  <si>
-    <t>Auto 6021389</t>
+    <t>Abdullah</t>
+  </si>
+  <si>
+    <t>Dickinson</t>
+  </si>
+  <si>
+    <t>Auto 39443903</t>
   </si>
   <si>
     <t>Department Manager_NEW</t>
@@ -514,16 +502,13 @@
     <t>Test9</t>
   </si>
   <si>
-    <t>10698074</t>
-  </si>
-  <si>
-    <t>Lindsey</t>
-  </si>
-  <si>
-    <t>Hagenes</t>
-  </si>
-  <si>
-    <t>Auto 51830818</t>
+    <t>Christa</t>
+  </si>
+  <si>
+    <t>Balistreri</t>
+  </si>
+  <si>
+    <t>Auto 7597421</t>
   </si>
   <si>
     <t>In-Store P&amp;C Manager_NEW</t>
@@ -532,13 +517,10 @@
     <t>Test10</t>
   </si>
   <si>
-    <t>10698075</t>
-  </si>
-  <si>
-    <t>Emmalee</t>
-  </si>
-  <si>
-    <t>Kertzmann</t>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>West</t>
   </si>
   <si>
     <t>In-Store P&amp;C Supervisor_NEW</t>
@@ -553,13 +535,10 @@
     <t>Test11</t>
   </si>
   <si>
-    <t>10698076</t>
-  </si>
-  <si>
-    <t>Ella</t>
-  </si>
-  <si>
-    <t>Jakubowski</t>
+    <t>Caterina</t>
+  </si>
+  <si>
+    <t>Dooley</t>
   </si>
   <si>
     <t>Supervisor_NEW</t>
@@ -571,13 +550,10 @@
     <t>Test12</t>
   </si>
   <si>
-    <t>10698078</t>
-  </si>
-  <si>
-    <t>Noelia</t>
-  </si>
-  <si>
-    <t>Cormier</t>
+    <t>Maryjane</t>
+  </si>
+  <si>
+    <t>Dietrich</t>
   </si>
   <si>
     <t>Retail Assistant Cash Office_NEW</t>
@@ -589,19 +565,10 @@
     <t>Test13</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Jared Monahan' Employee:{10698079}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('text=Onboarding Guide: Visual Merchandiser_NEW - Jared Monahan')[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Jared</t>
-  </si>
-  <si>
-    <t>Monahan</t>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>Stehr</t>
   </si>
   <si>
     <t>Visual Merchandiser_NEW</t>
@@ -610,16 +577,10 @@
     <t>Test14</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Declan West' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('Work Shift')[22m
-</t>
-  </si>
-  <si>
-    <t>Declan</t>
-  </si>
-  <si>
-    <t>West</t>
+    <t>Dawson</t>
+  </si>
+  <si>
+    <t>Maggio</t>
   </si>
   <si>
     <t>Retail Assistant Stockroom_NEW</t>
@@ -631,14 +592,10 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>Test failed for 'Ola Franecki' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.
-- Grade Profile is Missing     (Employee Compensation Event For Hire Employee)Alerts &amp; find failed Screenshot Path:-&gt;H:\WorkdaySuite_Playwright_latestcode/WorkdayFailedScreenshot/2025-03-21T14-37-45-106Z.png</t>
-  </si>
-  <si>
-    <t>Ola</t>
-  </si>
-  <si>
-    <t>Franecki</t>
+    <t>Nigel</t>
+  </si>
+  <si>
+    <t>McClure</t>
   </si>
   <si>
     <t>In-Store Visual Merchandising Supervisor_NEW</t>
@@ -737,7 +694,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1560,7 +1517,7 @@
       </c>
       <c r="K2" s="17">
         <f t="shared" ref="K2:K16" ca="1" si="0">TODAY()-7</f>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L2" s="13" t="s">
         <v>74</v>
@@ -1591,7 +1548,7 @@
       </c>
       <c r="U2" s="22">
         <f t="shared" ref="U2:U16" ca="1" si="1">TODAY()-31</f>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V2" s="16" t="s">
         <v>84</v>
@@ -1637,15 +1594,15 @@
       </c>
       <c r="AJ2" s="17">
         <f t="shared" ref="AJ2:AL16" ca="1" si="2">TODAY()-31</f>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK2" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL2" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM2" s="22" t="str">
         <f t="shared" ref="AM2:AM16" si="3">AF2</f>
@@ -1674,7 +1631,7 @@
       </c>
       <c r="AU2" s="17">
         <f t="shared" ref="AU2:AU16" ca="1" si="4">TODAY()+7</f>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV2" s="13" t="s">
         <v>74</v>
@@ -1684,7 +1641,7 @@
       </c>
       <c r="AX2" s="30">
         <f t="array" aca="1" ref="AX2:AX16" ca="1">_xlfn.RANDARRAY(15,1,1023456789000,9999999999999,TRUE)</f>
-        <v>5879589174643</v>
+        <v>3685585667530</v>
       </c>
       <c r="AY2" s="17" t="s">
         <v>98</v>
@@ -1700,7 +1657,7 @@
       </c>
       <c r="BC2" s="31">
         <f t="array" aca="1" ref="BC2:BC16" ca="1">_xlfn.RANDARRAY(15,1,12345678,99999999,TRUE)</f>
-        <v>90217606</v>
+        <v>81465916</v>
       </c>
       <c r="BD2" s="17" t="s">
         <v>98</v>
@@ -1743,7 +1700,7 @@
       </c>
       <c r="BQ2" s="34">
         <f t="array" aca="1" ref="BQ2:BQ16" ca="1">_xlfn.RANDARRAY(15,1,12345,99999,TRUE)</f>
-        <v>24175</v>
+        <v>38620</v>
       </c>
       <c r="BR2" s="17">
         <v>44562</v>
@@ -1756,7 +1713,7 @@
       </c>
       <c r="BU2" s="22">
         <f t="shared" ref="BU2:BU16" ca="1" si="5">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV2" s="16" t="s">
         <v>109</v>
@@ -1770,19 +1727,19 @@
         <v>111</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>74</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>77</v>
@@ -1795,7 +1752,7 @@
       </c>
       <c r="K3" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>74</v>
@@ -1826,19 +1783,19 @@
       </c>
       <c r="U3" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V3" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X3" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z3" s="24" t="s">
         <v>88</v>
@@ -1872,25 +1829,25 @@
       </c>
       <c r="AJ3" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK3" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL3" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM3" s="22" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN3" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO3" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AP3" s="24" t="s">
         <v>94</v>
@@ -1909,7 +1866,7 @@
       </c>
       <c r="AU3" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV3" s="13" t="s">
         <v>74</v>
@@ -1919,7 +1876,7 @@
       </c>
       <c r="AX3" s="30">
         <f ca="1"/>
-        <v>9629308524529</v>
+        <v>3276584545764</v>
       </c>
       <c r="AY3" s="17" t="s">
         <v>98</v>
@@ -1935,7 +1892,7 @@
       </c>
       <c r="BC3" s="31">
         <f ca="1"/>
-        <v>32599431</v>
+        <v>87692791</v>
       </c>
       <c r="BD3" s="17" t="s">
         <v>98</v>
@@ -1978,7 +1935,7 @@
       </c>
       <c r="BQ3" s="34">
         <f ca="1"/>
-        <v>30782</v>
+        <v>89330</v>
       </c>
       <c r="BR3" s="17">
         <v>44562</v>
@@ -1991,7 +1948,7 @@
       </c>
       <c r="BU3" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV3" s="16" t="s">
         <v>109</v>
@@ -1999,14 +1956,9 @@
     </row>
     <row r="4" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>72</v>
-      </c>
+      <c r="C4" s="11"/>
       <c r="D4" s="12" t="s">
         <v>121</v>
       </c>
@@ -2030,7 +1982,7 @@
       </c>
       <c r="K4" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>74</v>
@@ -2061,19 +2013,19 @@
       </c>
       <c r="U4" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V4" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W4" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X4" s="24" t="s">
         <v>124</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z4" s="24" t="s">
         <v>125</v>
@@ -2095,7 +2047,7 @@
       </c>
       <c r="AF4" s="28">
         <f ca="1">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AG4" s="16" t="s">
         <v>92</v>
@@ -2108,25 +2060,25 @@
       </c>
       <c r="AJ4" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK4" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL4" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM4" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AN4" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO4" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AP4" s="24" t="s">
         <v>94</v>
@@ -2145,7 +2097,7 @@
       </c>
       <c r="AU4" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV4" s="13" t="s">
         <v>74</v>
@@ -2155,7 +2107,7 @@
       </c>
       <c r="AX4" s="30">
         <f ca="1"/>
-        <v>4535670695535</v>
+        <v>8801576696517</v>
       </c>
       <c r="AY4" s="17" t="s">
         <v>98</v>
@@ -2171,7 +2123,7 @@
       </c>
       <c r="BC4" s="31">
         <f ca="1"/>
-        <v>57464761</v>
+        <v>59944209</v>
       </c>
       <c r="BD4" s="17" t="s">
         <v>98</v>
@@ -2214,7 +2166,7 @@
       </c>
       <c r="BQ4" s="34">
         <f ca="1"/>
-        <v>41501</v>
+        <v>58285</v>
       </c>
       <c r="BR4" s="17">
         <v>44562</v>
@@ -2227,7 +2179,7 @@
       </c>
       <c r="BU4" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV4" s="16" t="s">
         <v>109</v>
@@ -2237,14 +2189,9 @@
       <c r="A5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>74</v>
@@ -2266,7 +2213,7 @@
       </c>
       <c r="K5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L5" s="13" t="s">
         <v>74</v>
@@ -2297,7 +2244,7 @@
       </c>
       <c r="U5" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V5" s="16" t="s">
         <v>84</v>
@@ -2331,7 +2278,7 @@
       </c>
       <c r="AF5" s="28">
         <f ca="1">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AG5" s="16" t="s">
         <v>92</v>
@@ -2344,19 +2291,19 @@
       </c>
       <c r="AJ5" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK5" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL5" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM5" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AN5" s="16">
         <v>92</v>
@@ -2381,7 +2328,7 @@
       </c>
       <c r="AU5" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV5" s="13" t="s">
         <v>74</v>
@@ -2391,7 +2338,7 @@
       </c>
       <c r="AX5" s="30">
         <f ca="1"/>
-        <v>6805196517561</v>
+        <v>6140828842973</v>
       </c>
       <c r="AY5" s="17" t="s">
         <v>98</v>
@@ -2407,7 +2354,7 @@
       </c>
       <c r="BC5" s="31">
         <f ca="1"/>
-        <v>70131589</v>
+        <v>32827739</v>
       </c>
       <c r="BD5" s="17" t="s">
         <v>98</v>
@@ -2450,7 +2397,7 @@
       </c>
       <c r="BQ5" s="34">
         <f ca="1"/>
-        <v>57465</v>
+        <v>93929</v>
       </c>
       <c r="BR5" s="17">
         <v>44562</v>
@@ -2463,7 +2410,7 @@
       </c>
       <c r="BU5" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV5" s="16" t="s">
         <v>109</v>
@@ -2473,12 +2420,7 @@
       <c r="A6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>72</v>
-      </c>
+      <c r="C6" s="11"/>
       <c r="D6" s="12" t="s">
         <v>121</v>
       </c>
@@ -2486,10 +2428,10 @@
         <v>74</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>77</v>
@@ -2502,7 +2444,7 @@
       </c>
       <c r="K6" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L6" s="13" t="s">
         <v>74</v>
@@ -2533,19 +2475,19 @@
       </c>
       <c r="U6" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V6" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W6" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X6" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y6" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Z6" s="24" t="s">
         <v>88</v>
@@ -2579,25 +2521,25 @@
       </c>
       <c r="AJ6" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK6" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL6" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM6" s="22" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN6" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO6" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP6" s="24" t="s">
         <v>94</v>
@@ -2616,7 +2558,7 @@
       </c>
       <c r="AU6" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV6" s="13" t="s">
         <v>74</v>
@@ -2626,7 +2568,7 @@
       </c>
       <c r="AX6" s="30">
         <f ca="1"/>
-        <v>3129804546869</v>
+        <v>7349315343891</v>
       </c>
       <c r="AY6" s="17" t="s">
         <v>98</v>
@@ -2642,7 +2584,7 @@
       </c>
       <c r="BC6" s="31">
         <f ca="1"/>
-        <v>85197506</v>
+        <v>33693281</v>
       </c>
       <c r="BD6" s="17" t="s">
         <v>98</v>
@@ -2685,7 +2627,7 @@
       </c>
       <c r="BQ6" s="34">
         <f ca="1"/>
-        <v>34673</v>
+        <v>19934</v>
       </c>
       <c r="BR6" s="17">
         <v>44562</v>
@@ -2698,7 +2640,7 @@
       </c>
       <c r="BU6" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV6" s="16" t="s">
         <v>109</v>
@@ -2706,25 +2648,20 @@
     </row>
     <row r="7" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="G7" s="14" t="s">
         <v>142</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>144</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>77</v>
@@ -2737,7 +2674,7 @@
       </c>
       <c r="K7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>74</v>
@@ -2768,13 +2705,13 @@
       </c>
       <c r="U7" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V7" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W7" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="X7" s="24" t="s">
         <v>86</v>
@@ -2814,15 +2751,15 @@
       </c>
       <c r="AJ7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM7" s="22" t="str">
         <f t="shared" si="3"/>
@@ -2838,10 +2775,10 @@
         <v>94</v>
       </c>
       <c r="AQ7" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AS7" s="13" t="s">
         <v>90</v>
@@ -2851,7 +2788,7 @@
       </c>
       <c r="AU7" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV7" s="13" t="s">
         <v>74</v>
@@ -2861,7 +2798,7 @@
       </c>
       <c r="AX7" s="30">
         <f ca="1"/>
-        <v>3882424946312</v>
+        <v>3621529537223</v>
       </c>
       <c r="AY7" s="17" t="s">
         <v>98</v>
@@ -2877,7 +2814,7 @@
       </c>
       <c r="BC7" s="31">
         <f ca="1"/>
-        <v>89025441</v>
+        <v>14511938</v>
       </c>
       <c r="BD7" s="17" t="s">
         <v>98</v>
@@ -2920,7 +2857,7 @@
       </c>
       <c r="BQ7" s="34">
         <f ca="1"/>
-        <v>15689</v>
+        <v>56524</v>
       </c>
       <c r="BR7" s="17">
         <v>44562</v>
@@ -2933,7 +2870,7 @@
       </c>
       <c r="BU7" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV7" s="16" t="s">
         <v>109</v>
@@ -2941,25 +2878,21 @@
     </row>
     <row r="8" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>148</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>151</v>
       </c>
       <c r="H8" s="39" t="s">
         <v>77</v>
@@ -2972,7 +2905,7 @@
       </c>
       <c r="K8" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L8" s="34" t="s">
         <v>74</v>
@@ -3003,19 +2936,19 @@
       </c>
       <c r="U8" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V8" s="40" t="s">
         <v>84</v>
       </c>
       <c r="W8" s="40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="X8" s="47" t="s">
         <v>124</v>
       </c>
       <c r="Y8" s="47" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Z8" s="47" t="s">
         <v>88</v>
@@ -3037,7 +2970,7 @@
       </c>
       <c r="AF8" s="50">
         <f ca="1">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AG8" s="40" t="s">
         <v>92</v>
@@ -3050,19 +2983,19 @@
       </c>
       <c r="AJ8" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK8" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL8" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM8" s="46">
         <f t="shared" ca="1" si="3"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AN8" s="40">
         <v>92</v>
@@ -3074,10 +3007,10 @@
         <v>94</v>
       </c>
       <c r="AQ8" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AR8" s="43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AS8" s="34" t="s">
         <v>90</v>
@@ -3087,7 +3020,7 @@
       </c>
       <c r="AU8" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV8" s="34" t="s">
         <v>74</v>
@@ -3097,7 +3030,7 @@
       </c>
       <c r="AX8" s="30">
         <f ca="1"/>
-        <v>9824543293334</v>
+        <v>3508206066558</v>
       </c>
       <c r="AY8" s="41" t="s">
         <v>98</v>
@@ -3113,7 +3046,7 @@
       </c>
       <c r="BC8" s="31">
         <f ca="1"/>
-        <v>18676007</v>
+        <v>78816507</v>
       </c>
       <c r="BD8" s="41" t="s">
         <v>98</v>
@@ -3156,7 +3089,7 @@
       </c>
       <c r="BQ8" s="34">
         <f ca="1"/>
-        <v>75678</v>
+        <v>63924</v>
       </c>
       <c r="BR8" s="41">
         <v>44562</v>
@@ -3169,7 +3102,7 @@
       </c>
       <c r="BU8" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV8" s="40" t="s">
         <v>109</v>
@@ -3177,25 +3110,21 @@
     </row>
     <row r="9" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="37" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>74</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H9" s="39" t="s">
         <v>77</v>
@@ -3208,7 +3137,7 @@
       </c>
       <c r="K9" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L9" s="34" t="s">
         <v>74</v>
@@ -3239,19 +3168,19 @@
       </c>
       <c r="U9" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V9" s="40" t="s">
         <v>84</v>
       </c>
       <c r="W9" s="40" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="X9" s="47" t="s">
         <v>86</v>
       </c>
       <c r="Y9" s="47" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="Z9" s="47" t="s">
         <v>125</v>
@@ -3285,15 +3214,15 @@
       </c>
       <c r="AJ9" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK9" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL9" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM9" s="46" t="str">
         <f t="shared" si="3"/>
@@ -3309,10 +3238,10 @@
         <v>94</v>
       </c>
       <c r="AQ9" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AR9" s="43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AS9" s="34" t="s">
         <v>90</v>
@@ -3322,7 +3251,7 @@
       </c>
       <c r="AU9" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV9" s="34" t="s">
         <v>74</v>
@@ -3332,7 +3261,7 @@
       </c>
       <c r="AX9" s="30">
         <f ca="1"/>
-        <v>6574353571659</v>
+        <v>3874603468215</v>
       </c>
       <c r="AY9" s="41" t="s">
         <v>98</v>
@@ -3348,7 +3277,7 @@
       </c>
       <c r="BC9" s="31">
         <f ca="1"/>
-        <v>78589868</v>
+        <v>57432686</v>
       </c>
       <c r="BD9" s="41" t="s">
         <v>98</v>
@@ -3391,7 +3320,7 @@
       </c>
       <c r="BQ9" s="34">
         <f ca="1"/>
-        <v>51690</v>
+        <v>98286</v>
       </c>
       <c r="BR9" s="41">
         <v>44562</v>
@@ -3404,7 +3333,7 @@
       </c>
       <c r="BU9" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV9" s="40" t="s">
         <v>109</v>
@@ -3412,25 +3341,20 @@
     </row>
     <row r="10" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C10" s="11"/>
       <c r="D10" s="12" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>74</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>77</v>
@@ -3443,7 +3367,7 @@
       </c>
       <c r="K10" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L10" s="13" t="s">
         <v>74</v>
@@ -3474,19 +3398,19 @@
       </c>
       <c r="U10" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V10" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W10" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="X10" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y10" s="24" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Z10" s="24" t="s">
         <v>88</v>
@@ -3520,15 +3444,15 @@
       </c>
       <c r="AJ10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM10" s="22" t="str">
         <f t="shared" si="3"/>
@@ -3544,10 +3468,10 @@
         <v>94</v>
       </c>
       <c r="AQ10" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AR10" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AS10" s="13" t="s">
         <v>90</v>
@@ -3557,7 +3481,7 @@
       </c>
       <c r="AU10" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV10" s="13" t="s">
         <v>74</v>
@@ -3567,7 +3491,7 @@
       </c>
       <c r="AX10" s="30">
         <f ca="1"/>
-        <v>3850767557935</v>
+        <v>4474505969211</v>
       </c>
       <c r="AY10" s="17" t="s">
         <v>98</v>
@@ -3583,7 +3507,7 @@
       </c>
       <c r="BC10" s="31">
         <f ca="1"/>
-        <v>74805827</v>
+        <v>21966030</v>
       </c>
       <c r="BD10" s="17" t="s">
         <v>98</v>
@@ -3626,7 +3550,7 @@
       </c>
       <c r="BQ10" s="34">
         <f ca="1"/>
-        <v>84181</v>
+        <v>64701</v>
       </c>
       <c r="BR10" s="17">
         <v>44562</v>
@@ -3639,7 +3563,7 @@
       </c>
       <c r="BU10" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV10" s="16" t="s">
         <v>109</v>
@@ -3647,14 +3571,10 @@
     </row>
     <row r="11" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="37" t="s">
         <v>121</v>
       </c>
@@ -3662,10 +3582,10 @@
         <v>74</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H11" s="39" t="s">
         <v>77</v>
@@ -3678,7 +3598,7 @@
       </c>
       <c r="K11" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L11" s="34" t="s">
         <v>74</v>
@@ -3709,19 +3629,19 @@
       </c>
       <c r="U11" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V11" s="40" t="s">
         <v>84</v>
       </c>
       <c r="W11" s="40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X11" s="47" t="s">
         <v>86</v>
       </c>
       <c r="Y11" s="47" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="Z11" s="47" t="s">
         <v>88</v>
@@ -3755,31 +3675,31 @@
       </c>
       <c r="AJ11" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM11" s="46" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN11" s="40" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO11" s="47" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AP11" s="47" t="s">
         <v>94</v>
       </c>
       <c r="AQ11" s="47" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AR11" s="43" t="s">
         <v>96</v>
@@ -3792,7 +3712,7 @@
       </c>
       <c r="AU11" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV11" s="34" t="s">
         <v>74</v>
@@ -3802,7 +3722,7 @@
       </c>
       <c r="AX11" s="30">
         <f ca="1"/>
-        <v>8820339871414</v>
+        <v>8301372478441</v>
       </c>
       <c r="AY11" s="41" t="s">
         <v>98</v>
@@ -3818,7 +3738,7 @@
       </c>
       <c r="BC11" s="31">
         <f ca="1"/>
-        <v>14120630</v>
+        <v>26107089</v>
       </c>
       <c r="BD11" s="41" t="s">
         <v>98</v>
@@ -3861,7 +3781,7 @@
       </c>
       <c r="BQ11" s="34">
         <f ca="1"/>
-        <v>56854</v>
+        <v>65536</v>
       </c>
       <c r="BR11" s="41">
         <v>44562</v>
@@ -3874,7 +3794,7 @@
       </c>
       <c r="BU11" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV11" s="40" t="s">
         <v>109</v>
@@ -3882,14 +3802,9 @@
     </row>
     <row r="12" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
         <v>121</v>
       </c>
@@ -3897,10 +3812,10 @@
         <v>74</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>77</v>
@@ -3913,7 +3828,7 @@
       </c>
       <c r="K12" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>74</v>
@@ -3944,19 +3859,19 @@
       </c>
       <c r="U12" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V12" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W12" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X12" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Z12" s="24" t="s">
         <v>125</v>
@@ -3990,31 +3905,31 @@
       </c>
       <c r="AJ12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM12" s="22" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN12" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AP12" s="24" t="s">
         <v>94</v>
       </c>
       <c r="AQ12" s="24" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AR12" s="19" t="s">
         <v>96</v>
@@ -4027,7 +3942,7 @@
       </c>
       <c r="AU12" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV12" s="13" t="s">
         <v>74</v>
@@ -4037,7 +3952,7 @@
       </c>
       <c r="AX12" s="30">
         <f ca="1"/>
-        <v>6329089829318</v>
+        <v>8071851508394</v>
       </c>
       <c r="AY12" s="17" t="s">
         <v>98</v>
@@ -4053,7 +3968,7 @@
       </c>
       <c r="BC12" s="31">
         <f ca="1"/>
-        <v>44951213</v>
+        <v>33545930</v>
       </c>
       <c r="BD12" s="17" t="s">
         <v>98</v>
@@ -4096,7 +4011,7 @@
       </c>
       <c r="BQ12" s="34">
         <f ca="1"/>
-        <v>35567</v>
+        <v>69630</v>
       </c>
       <c r="BR12" s="17">
         <v>44562</v>
@@ -4109,7 +4024,7 @@
       </c>
       <c r="BU12" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV12" s="16" t="s">
         <v>109</v>
@@ -4117,14 +4032,10 @@
     </row>
     <row r="13" spans="1:74" s="35" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>72</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="37" t="s">
         <v>121</v>
       </c>
@@ -4132,10 +4043,10 @@
         <v>74</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H13" s="39" t="s">
         <v>77</v>
@@ -4148,7 +4059,7 @@
       </c>
       <c r="K13" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L13" s="34" t="s">
         <v>74</v>
@@ -4179,19 +4090,19 @@
       </c>
       <c r="U13" s="46">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V13" s="40" t="s">
         <v>84</v>
       </c>
       <c r="W13" s="40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X13" s="47" t="s">
         <v>124</v>
       </c>
       <c r="Y13" s="47" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="Z13" s="47" t="s">
         <v>125</v>
@@ -4213,7 +4124,7 @@
       </c>
       <c r="AF13" s="50">
         <f ca="1">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AG13" s="40" t="s">
         <v>92</v>
@@ -4226,25 +4137,25 @@
       </c>
       <c r="AJ13" s="41">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK13" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL13" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM13" s="46">
         <f t="shared" ca="1" si="3"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AN13" s="40" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO13" s="47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AP13" s="47" t="s">
         <v>94</v>
@@ -4263,7 +4174,7 @@
       </c>
       <c r="AU13" s="41">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV13" s="34" t="s">
         <v>74</v>
@@ -4273,7 +4184,7 @@
       </c>
       <c r="AX13" s="30">
         <f ca="1"/>
-        <v>3437783974897</v>
+        <v>2601554379503</v>
       </c>
       <c r="AY13" s="41" t="s">
         <v>98</v>
@@ -4289,7 +4200,7 @@
       </c>
       <c r="BC13" s="31">
         <f ca="1"/>
-        <v>64831588</v>
+        <v>29368358</v>
       </c>
       <c r="BD13" s="41" t="s">
         <v>98</v>
@@ -4332,7 +4243,7 @@
       </c>
       <c r="BQ13" s="34">
         <f ca="1"/>
-        <v>18196</v>
+        <v>63503</v>
       </c>
       <c r="BR13" s="41">
         <v>44562</v>
@@ -4345,7 +4256,7 @@
       </c>
       <c r="BU13" s="46">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV13" s="40" t="s">
         <v>109</v>
@@ -4353,14 +4264,10 @@
     </row>
     <row r="14" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>187</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="12" t="s">
         <v>121</v>
       </c>
@@ -4368,10 +4275,10 @@
         <v>74</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>77</v>
@@ -4384,7 +4291,7 @@
       </c>
       <c r="K14" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>74</v>
@@ -4415,19 +4322,19 @@
       </c>
       <c r="U14" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V14" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W14" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X14" s="24" t="s">
         <v>124</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="Z14" s="24" t="s">
         <v>88</v>
@@ -4449,7 +4356,7 @@
       </c>
       <c r="AF14" s="28">
         <f ca="1">TODAY()+365</f>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AG14" s="16" t="s">
         <v>92</v>
@@ -4462,25 +4369,25 @@
       </c>
       <c r="AJ14" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK14" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL14" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM14" s="22">
         <f t="shared" ca="1" si="3"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AN14" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO14" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP14" s="24" t="s">
         <v>94</v>
@@ -4499,7 +4406,7 @@
       </c>
       <c r="AU14" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV14" s="13" t="s">
         <v>74</v>
@@ -4509,7 +4416,7 @@
       </c>
       <c r="AX14" s="30">
         <f ca="1"/>
-        <v>3941794048959</v>
+        <v>8862074638158</v>
       </c>
       <c r="AY14" s="17" t="s">
         <v>98</v>
@@ -4525,7 +4432,7 @@
       </c>
       <c r="BC14" s="31">
         <f ca="1"/>
-        <v>82567804</v>
+        <v>86306078</v>
       </c>
       <c r="BD14" s="17" t="s">
         <v>98</v>
@@ -4568,7 +4475,7 @@
       </c>
       <c r="BQ14" s="34">
         <f ca="1"/>
-        <v>35646</v>
+        <v>32606</v>
       </c>
       <c r="BR14" s="17">
         <v>44562</v>
@@ -4581,7 +4488,7 @@
       </c>
       <c r="BU14" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV14" s="16" t="s">
         <v>109</v>
@@ -4589,14 +4496,9 @@
     </row>
     <row r="15" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>187</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C15" s="11"/>
       <c r="D15" s="12" t="s">
         <v>121</v>
       </c>
@@ -4604,10 +4506,10 @@
         <v>74</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>77</v>
@@ -4620,7 +4522,7 @@
       </c>
       <c r="K15" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>74</v>
@@ -4651,19 +4553,19 @@
       </c>
       <c r="U15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V15" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W15" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X15" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y15" s="24" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="Z15" s="24" t="s">
         <v>125</v>
@@ -4697,25 +4599,25 @@
       </c>
       <c r="AJ15" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK15" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL15" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM15" s="22" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN15" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO15" s="24" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="AP15" s="24" t="s">
         <v>94</v>
@@ -4734,7 +4636,7 @@
       </c>
       <c r="AU15" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV15" s="13" t="s">
         <v>74</v>
@@ -4744,7 +4646,7 @@
       </c>
       <c r="AX15" s="30">
         <f ca="1"/>
-        <v>6519217663694</v>
+        <v>3201856004603</v>
       </c>
       <c r="AY15" s="17" t="s">
         <v>98</v>
@@ -4760,7 +4662,7 @@
       </c>
       <c r="BC15" s="31">
         <f ca="1"/>
-        <v>61320857</v>
+        <v>94568555</v>
       </c>
       <c r="BD15" s="17" t="s">
         <v>98</v>
@@ -4803,7 +4705,7 @@
       </c>
       <c r="BQ15" s="34">
         <f ca="1"/>
-        <v>75176</v>
+        <v>95267</v>
       </c>
       <c r="BR15" s="17">
         <v>44562</v>
@@ -4816,7 +4718,7 @@
       </c>
       <c r="BU15" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV15" s="16" t="s">
         <v>109</v>
@@ -4824,14 +4726,10 @@
     </row>
     <row r="16" spans="1:74" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>187</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="12" t="s">
         <v>121</v>
       </c>
@@ -4839,10 +4737,10 @@
         <v>74</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>77</v>
@@ -4855,7 +4753,7 @@
       </c>
       <c r="K16" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>74</v>
@@ -4886,19 +4784,19 @@
       </c>
       <c r="U16" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="V16" s="16" t="s">
         <v>84</v>
       </c>
       <c r="W16" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X16" s="24" t="s">
         <v>86</v>
       </c>
       <c r="Y16" s="24" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="Z16" s="24" t="s">
         <v>88</v>
@@ -4932,31 +4830,31 @@
       </c>
       <c r="AJ16" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AK16" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AL16" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45709</v>
+        <v>45710</v>
       </c>
       <c r="AM16" s="22" t="str">
         <f t="shared" si="3"/>
         <v>N/A</v>
       </c>
       <c r="AN16" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AO16" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP16" s="24" t="s">
         <v>94</v>
       </c>
       <c r="AQ16" s="24" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="AR16" s="19" t="s">
         <v>96</v>
@@ -4969,7 +4867,7 @@
       </c>
       <c r="AU16" s="17">
         <f t="shared" ca="1" si="4"/>
-        <v>45747</v>
+        <v>45748</v>
       </c>
       <c r="AV16" s="13" t="s">
         <v>74</v>
@@ -4979,7 +4877,7 @@
       </c>
       <c r="AX16" s="30">
         <f ca="1"/>
-        <v>5300785576112</v>
+        <v>1348904031879</v>
       </c>
       <c r="AY16" s="17" t="s">
         <v>98</v>
@@ -4995,7 +4893,7 @@
       </c>
       <c r="BC16" s="31">
         <f ca="1"/>
-        <v>85925571</v>
+        <v>35193303</v>
       </c>
       <c r="BD16" s="17" t="s">
         <v>98</v>
@@ -5038,7 +4936,7 @@
       </c>
       <c r="BQ16" s="34">
         <f ca="1"/>
-        <v>46500</v>
+        <v>38041</v>
       </c>
       <c r="BR16" s="17">
         <v>44562</v>
@@ -5051,17 +4949,17 @@
       </c>
       <c r="BU16" s="22">
         <f t="shared" ca="1" si="5"/>
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="BV16" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AF17" s="54"/>
       <c r="AL17" s="17"/>
     </row>
-    <row r="18" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="32:38" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AL18" s="17"/>
     </row>
   </sheetData>
